--- a/Översikt JOKKMOKK.xlsx
+++ b/Översikt JOKKMOKK.xlsx
@@ -601,7 +601,7 @@
         <v>45680</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -766,7 +766,7 @@
         <v>45971</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -918,7 +918,7 @@
         <v>46230</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1067,7 +1067,7 @@
         <v>46043</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1205,7 +1205,7 @@
         <v>46184</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1346,7 +1346,7 @@
         <v>46177</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1486,7 +1486,7 @@
         <v>44917</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1624,7 +1624,7 @@
         <v>44539</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1760,7 +1760,7 @@
         <v>46244</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1896,7 +1896,7 @@
         <v>44824</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>45222</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2165,7 +2165,7 @@
         <v>45672</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2297,7 +2297,7 @@
         <v>45805</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2429,7 +2429,7 @@
         <v>46010</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2556,7 +2556,7 @@
         <v>44781</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2683,7 +2683,7 @@
         <v>45476</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2810,7 +2810,7 @@
         <v>45985</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2937,7 +2937,7 @@
         <v>45237</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -3068,7 +3068,7 @@
         <v>45649</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3197,7 +3197,7 @@
         <v>45993</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3321,7 +3321,7 @@
         <v>45484</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3448,7 +3448,7 @@
         <v>44474</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3579,7 +3579,7 @@
         <v>44722</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3702,7 +3702,7 @@
         <v>45174</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3829,7 +3829,7 @@
         <v>45672</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3956,7 +3956,7 @@
         <v>44552</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -4075,7 +4075,7 @@
         <v>45649</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -4199,7 +4199,7 @@
         <v>45994</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4318,7 +4318,7 @@
         <v>45986</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4437,7 +4437,7 @@
         <v>45596</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4560,7 +4560,7 @@
         <v>46184</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4683,7 +4683,7 @@
         <v>45476</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4801,7 +4801,7 @@
         <v>45810</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4918,7 +4918,7 @@
         <v>45113</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -5036,7 +5036,7 @@
         <v>46283</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -5158,7 +5158,7 @@
         <v>46042</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -5279,7 +5279,7 @@
         <v>45940</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5395,7 +5395,7 @@
         <v>46184</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5511,7 +5511,7 @@
         <v>46101</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5626,7 +5626,7 @@
         <v>44722</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5741,7 +5741,7 @@
         <v>46149</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5851,7 +5851,7 @@
         <v>44490</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5965,7 +5965,7 @@
         <v>45484</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -6079,7 +6079,7 @@
         <v>45609</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -6197,7 +6197,7 @@
         <v>46184</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -6311,7 +6311,7 @@
         <v>46090</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6420,7 +6420,7 @@
         <v>46113</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6533,7 +6533,7 @@
         <v>45170</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6646,7 +6646,7 @@
         <v>46206</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6754,7 +6754,7 @@
         <v>46213</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6866,7 +6866,7 @@
         <v>45114</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6979,7 +6979,7 @@
         <v>46013</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -7091,7 +7091,7 @@
         <v>45134</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -7198,7 +7198,7 @@
         <v>45649</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -7314,7 +7314,7 @@
         <v>44545</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -7421,7 +7421,7 @@
         <v>45748</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7528,7 +7528,7 @@
         <v>45012</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7635,7 +7635,7 @@
         <v>44825</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7751,7 +7751,7 @@
         <v>44810</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7861,7 +7861,7 @@
         <v>44726</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7972,7 +7972,7 @@
         <v>44824</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -8083,7 +8083,7 @@
         <v>45891</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -8194,7 +8194,7 @@
         <v>45891</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -8309,7 +8309,7 @@
         <v>45897</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -8420,7 +8420,7 @@
         <v>45951</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8531,7 +8531,7 @@
         <v>45992</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8642,7 +8642,7 @@
         <v>46178</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8753,7 +8753,7 @@
         <v>46184</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8864,7 +8864,7 @@
         <v>45113</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8975,7 +8975,7 @@
         <v>46184</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -9086,7 +9086,7 @@
         <v>46213</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -9197,7 +9197,7 @@
         <v>46184</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -9308,7 +9308,7 @@
         <v>46261</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -9418,7 +9418,7 @@
         <v>45035</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -9529,7 +9529,7 @@
         <v>45225</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9639,7 +9639,7 @@
         <v>45222</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9744,7 +9744,7 @@
         <v>46027</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9849,7 +9849,7 @@
         <v>45799</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9963,7 +9963,7 @@
         <v>45919</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -10073,7 +10073,7 @@
         <v>45572</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -10183,7 +10183,7 @@
         <v>45944</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -10293,7 +10293,7 @@
         <v>45951</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -10403,7 +10403,7 @@
         <v>45958</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -10513,7 +10513,7 @@
         <v>45974</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -10623,7 +10623,7 @@
         <v>45974</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10733,7 +10733,7 @@
         <v>44545</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10838,7 +10838,7 @@
         <v>45982</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10952,7 +10952,7 @@
         <v>45985</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -11062,7 +11062,7 @@
         <v>46137</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -11172,7 +11172,7 @@
         <v>45819</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -11282,7 +11282,7 @@
         <v>45672</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -11392,7 +11392,7 @@
         <v>45826</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -11502,7 +11502,7 @@
         <v>44865</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -11616,7 +11616,7 @@
         <v>45838</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11726,7 +11726,7 @@
         <v>45608</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11836,7 +11836,7 @@
         <v>45600</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11941,7 +11941,7 @@
         <v>45876</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -12051,7 +12051,7 @@
         <v>46197</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -12161,7 +12161,7 @@
         <v>46199</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -12271,7 +12271,7 @@
         <v>46199</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -12381,7 +12381,7 @@
         <v>45915</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -12491,7 +12491,7 @@
         <v>46276</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -12601,7 +12601,7 @@
         <v>46240</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -12711,7 +12711,7 @@
         <v>45918</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -12816,7 +12816,7 @@
         <v>46272</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -12926,7 +12926,7 @@
         <v>44967</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -13036,7 +13036,7 @@
         <v>45358</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -13141,7 +13141,7 @@
         <v>44820</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -13219,7 +13219,7 @@
         <v>44676</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -13292,7 +13292,7 @@
         <v>44543</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -13370,7 +13370,7 @@
         <v>44543</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -13448,7 +13448,7 @@
         <v>44543</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -13521,7 +13521,7 @@
         <v>44586</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -13599,7 +13599,7 @@
         <v>44586</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -13677,7 +13677,7 @@
         <v>44663</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -13750,7 +13750,7 @@
         <v>44685</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -13828,7 +13828,7 @@
         <v>44539</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -13906,7 +13906,7 @@
         <v>44543</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -13984,7 +13984,7 @@
         <v>44543</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -14062,7 +14062,7 @@
         <v>44638</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -14140,7 +14140,7 @@
         <v>44743</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -14218,7 +14218,7 @@
         <v>44543</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -14296,7 +14296,7 @@
         <v>44586</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -14374,7 +14374,7 @@
         <v>44573</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -14452,7 +14452,7 @@
         <v>44820</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -14530,7 +14530,7 @@
         <v>44824</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -14608,7 +14608,7 @@
         <v>44532</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -14681,7 +14681,7 @@
         <v>44868</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -14759,7 +14759,7 @@
         <v>45086</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -14832,7 +14832,7 @@
         <v>44862</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -14905,7 +14905,7 @@
         <v>44841</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -14983,7 +14983,7 @@
         <v>44873</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -15061,7 +15061,7 @@
         <v>45113</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -15139,7 +15139,7 @@
         <v>44866</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -15217,7 +15217,7 @@
         <v>45106</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -15295,7 +15295,7 @@
         <v>44868</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -15368,7 +15368,7 @@
         <v>45474</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -15446,7 +15446,7 @@
         <v>45474</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -15524,7 +15524,7 @@
         <v>45474</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -15602,7 +15602,7 @@
         <v>45474</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -15680,7 +15680,7 @@
         <v>45474</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -15758,7 +15758,7 @@
         <v>45471</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -15836,7 +15836,7 @@
         <v>45463</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -15914,7 +15914,7 @@
         <v>45572</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -15992,7 +15992,7 @@
         <v>46021</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -16065,7 +16065,7 @@
         <v>46010</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -16138,7 +16138,7 @@
         <v>46010</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -16216,7 +16216,7 @@
         <v>46009</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -16289,7 +16289,7 @@
         <v>44966</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -16362,7 +16362,7 @@
         <v>45884</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -16440,7 +16440,7 @@
         <v>46030</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -16518,7 +16518,7 @@
         <v>45505</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -16596,7 +16596,7 @@
         <v>45994</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -16674,7 +16674,7 @@
         <v>45883</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -16752,7 +16752,7 @@
         <v>45992</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -16830,7 +16830,7 @@
         <v>45993</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -16908,7 +16908,7 @@
         <v>44477</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -16981,7 +16981,7 @@
         <v>44841</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -17059,7 +17059,7 @@
         <v>44984</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -17137,7 +17137,7 @@
         <v>45693</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -17210,7 +17210,7 @@
         <v>45544</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -17288,7 +17288,7 @@
         <v>45897</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -17366,7 +17366,7 @@
         <v>45073</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -17444,7 +17444,7 @@
         <v>45901</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -17522,7 +17522,7 @@
         <v>45904</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -17600,7 +17600,7 @@
         <v>45491</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -17673,7 +17673,7 @@
         <v>45883</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -17751,7 +17751,7 @@
         <v>45646</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -17824,7 +17824,7 @@
         <v>45907</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -17897,7 +17897,7 @@
         <v>45259</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -17975,7 +17975,7 @@
         <v>45572</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -18053,7 +18053,7 @@
         <v>45912</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -18131,7 +18131,7 @@
         <v>45558</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -18209,7 +18209,7 @@
         <v>45664</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -18287,7 +18287,7 @@
         <v>45491</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -18360,7 +18360,7 @@
         <v>45918</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -18438,7 +18438,7 @@
         <v>45572</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -18516,7 +18516,7 @@
         <v>45028</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -18589,7 +18589,7 @@
         <v>45596</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -18667,7 +18667,7 @@
         <v>46077</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -18745,7 +18745,7 @@
         <v>46077</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -18823,7 +18823,7 @@
         <v>46077</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -18901,7 +18901,7 @@
         <v>46077</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -18979,7 +18979,7 @@
         <v>45928</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -19057,7 +19057,7 @@
         <v>45887</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -19135,7 +19135,7 @@
         <v>44984</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -19213,7 +19213,7 @@
         <v>44984</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -19291,7 +19291,7 @@
         <v>45544</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -19369,7 +19369,7 @@
         <v>45532</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -19442,7 +19442,7 @@
         <v>44984</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -19515,7 +19515,7 @@
         <v>44984</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -19588,7 +19588,7 @@
         <v>45526</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -19661,7 +19661,7 @@
         <v>45586</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -19734,7 +19734,7 @@
         <v>46092</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -19812,7 +19812,7 @@
         <v>46092</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -19890,7 +19890,7 @@
         <v>46092</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -19968,7 +19968,7 @@
         <v>46092</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -20046,7 +20046,7 @@
         <v>45940</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -20124,7 +20124,7 @@
         <v>45943</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -20202,7 +20202,7 @@
         <v>45942</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -20280,7 +20280,7 @@
         <v>45942</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -20358,7 +20358,7 @@
         <v>45946</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -20436,7 +20436,7 @@
         <v>45590</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -20514,7 +20514,7 @@
         <v>45950</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -20587,7 +20587,7 @@
         <v>45596</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -20665,7 +20665,7 @@
         <v>45950</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -20738,7 +20738,7 @@
         <v>45951</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -20816,7 +20816,7 @@
         <v>45951</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -20894,7 +20894,7 @@
         <v>45951</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -20972,7 +20972,7 @@
         <v>45951</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -21050,7 +21050,7 @@
         <v>44984</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -21128,7 +21128,7 @@
         <v>45951</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -21206,7 +21206,7 @@
         <v>45951</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -21284,7 +21284,7 @@
         <v>45951</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -21362,7 +21362,7 @@
         <v>46106</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -21440,7 +21440,7 @@
         <v>46106</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -21518,7 +21518,7 @@
         <v>46106</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -21596,7 +21596,7 @@
         <v>45953</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -21674,7 +21674,7 @@
         <v>45953</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -21752,7 +21752,7 @@
         <v>45953</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -21830,7 +21830,7 @@
         <v>46108</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -21908,7 +21908,7 @@
         <v>46108</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -21986,7 +21986,7 @@
         <v>45953</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -22064,7 +22064,7 @@
         <v>46108</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -22142,7 +22142,7 @@
         <v>46113</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -22220,7 +22220,7 @@
         <v>46113</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -22298,7 +22298,7 @@
         <v>46113</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -22376,7 +22376,7 @@
         <v>46113</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -22454,7 +22454,7 @@
         <v>46113</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -22532,7 +22532,7 @@
         <v>46113</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -22610,7 +22610,7 @@
         <v>46114</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -22688,7 +22688,7 @@
         <v>45993</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -22766,7 +22766,7 @@
         <v>45960</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -22839,7 +22839,7 @@
         <v>45572</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -22917,7 +22917,7 @@
         <v>45964</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -22995,7 +22995,7 @@
         <v>45965</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -23073,7 +23073,7 @@
         <v>45565</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -23151,7 +23151,7 @@
         <v>45965</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -23229,7 +23229,7 @@
         <v>45968</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -23302,7 +23302,7 @@
         <v>45967</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -23375,7 +23375,7 @@
         <v>45813</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -23448,7 +23448,7 @@
         <v>45972</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -23526,7 +23526,7 @@
         <v>45971</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -23604,7 +23604,7 @@
         <v>44477</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -23677,7 +23677,7 @@
         <v>45974</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -23755,7 +23755,7 @@
         <v>45973</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -23833,7 +23833,7 @@
         <v>45974</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -23911,7 +23911,7 @@
         <v>45973</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -23989,7 +23989,7 @@
         <v>45974</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -24067,7 +24067,7 @@
         <v>45974</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -24145,7 +24145,7 @@
         <v>45974</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -24223,7 +24223,7 @@
         <v>45111</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -24296,7 +24296,7 @@
         <v>45974</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -24374,7 +24374,7 @@
         <v>45975</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -24447,7 +24447,7 @@
         <v>45975</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -24525,7 +24525,7 @@
         <v>46010</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -24598,7 +24598,7 @@
         <v>45979</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -24676,7 +24676,7 @@
         <v>45979</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -24754,7 +24754,7 @@
         <v>44802</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -24827,7 +24827,7 @@
         <v>45985</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -24905,7 +24905,7 @@
         <v>45590</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -24983,7 +24983,7 @@
         <v>45985</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -25061,7 +25061,7 @@
         <v>45973</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -25139,7 +25139,7 @@
         <v>45721</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -25212,7 +25212,7 @@
         <v>45994</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -25290,7 +25290,7 @@
         <v>45995</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -25368,7 +25368,7 @@
         <v>45995</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -25446,7 +25446,7 @@
         <v>45124</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -25524,7 +25524,7 @@
         <v>45488</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -25597,7 +25597,7 @@
         <v>45953</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -25675,7 +25675,7 @@
         <v>46006</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -25748,7 +25748,7 @@
         <v>46137</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -25826,7 +25826,7 @@
         <v>45028</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -25899,7 +25899,7 @@
         <v>45819</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -25977,7 +25977,7 @@
         <v>46010</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -26050,7 +26050,7 @@
         <v>45824</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -26123,7 +26123,7 @@
         <v>45826</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -26201,7 +26201,7 @@
         <v>45904</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -26274,7 +26274,7 @@
         <v>45827</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -26352,7 +26352,7 @@
         <v>45516</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -26430,7 +26430,7 @@
         <v>45022</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -26508,7 +26508,7 @@
         <v>45608</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -26581,7 +26581,7 @@
         <v>45903</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -26659,7 +26659,7 @@
         <v>46083</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -26732,7 +26732,7 @@
         <v>45842</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -26810,7 +26810,7 @@
         <v>45838</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -26888,7 +26888,7 @@
         <v>45474</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -26966,7 +26966,7 @@
         <v>46162</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -27044,7 +27044,7 @@
         <v>46164</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -27122,7 +27122,7 @@
         <v>45860</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -27195,7 +27195,7 @@
         <v>45824</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -27268,7 +27268,7 @@
         <v>45883</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -27346,7 +27346,7 @@
         <v>45078</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -27424,7 +27424,7 @@
         <v>44493</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -27502,7 +27502,7 @@
         <v>46170</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -27580,7 +27580,7 @@
         <v>46170</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -27653,7 +27653,7 @@
         <v>45807</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -27731,7 +27731,7 @@
         <v>45868</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -27804,7 +27804,7 @@
         <v>45124</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -27882,7 +27882,7 @@
         <v>46177</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -27960,7 +27960,7 @@
         <v>46177</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -28038,7 +28038,7 @@
         <v>46177</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -28116,7 +28116,7 @@
         <v>46177</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -28194,7 +28194,7 @@
         <v>46178</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -28272,7 +28272,7 @@
         <v>46183</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -28350,7 +28350,7 @@
         <v>44539</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -28428,7 +28428,7 @@
         <v>46185</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -28506,7 +28506,7 @@
         <v>45166</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -28579,7 +28579,7 @@
         <v>44984</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -28657,7 +28657,7 @@
         <v>44984</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -28735,7 +28735,7 @@
         <v>44984</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -28813,7 +28813,7 @@
         <v>44984</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -28886,7 +28886,7 @@
         <v>44984</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -28964,7 +28964,7 @@
         <v>46191</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -29042,7 +29042,7 @@
         <v>45124</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -29120,7 +29120,7 @@
         <v>46192</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -29198,7 +29198,7 @@
         <v>46191</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -29276,7 +29276,7 @@
         <v>45613</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -29349,7 +29349,7 @@
         <v>45678</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -29427,7 +29427,7 @@
         <v>46197</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -29505,7 +29505,7 @@
         <v>46197</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -29583,7 +29583,7 @@
         <v>45565</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -29656,7 +29656,7 @@
         <v>45880</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -29734,7 +29734,7 @@
         <v>46197</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -29812,7 +29812,7 @@
         <v>45986</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -29885,7 +29885,7 @@
         <v>46199</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -29963,7 +29963,7 @@
         <v>46199</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -30041,7 +30041,7 @@
         <v>46199</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -30119,7 +30119,7 @@
         <v>45224</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -30197,7 +30197,7 @@
         <v>46198</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -30270,7 +30270,7 @@
         <v>45555</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -30343,7 +30343,7 @@
         <v>45349</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -30416,7 +30416,7 @@
         <v>46205</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -30489,7 +30489,7 @@
         <v>46204</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -30567,7 +30567,7 @@
         <v>46205</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -30640,7 +30640,7 @@
         <v>46206</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -30713,7 +30713,7 @@
         <v>46206</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -30786,7 +30786,7 @@
         <v>46211</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -30864,7 +30864,7 @@
         <v>45604</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -30942,7 +30942,7 @@
         <v>46254</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -31020,7 +31020,7 @@
         <v>46215</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -31093,7 +31093,7 @@
         <v>46215</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -31166,7 +31166,7 @@
         <v>46255</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -31239,7 +31239,7 @@
         <v>46212</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -31317,7 +31317,7 @@
         <v>46253</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -31390,7 +31390,7 @@
         <v>46212</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -31468,7 +31468,7 @@
         <v>45520</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -31546,7 +31546,7 @@
         <v>46216</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -31619,7 +31619,7 @@
         <v>46175</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -31692,7 +31692,7 @@
         <v>46216</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -31765,7 +31765,7 @@
         <v>44851</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -31838,7 +31838,7 @@
         <v>46266</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -31916,7 +31916,7 @@
         <v>45257</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -31994,7 +31994,7 @@
         <v>45474</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -32072,7 +32072,7 @@
         <v>45763</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -32150,7 +32150,7 @@
         <v>46274</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -32228,7 +32228,7 @@
         <v>46009</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -32301,7 +32301,7 @@
         <v>46237</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -32374,7 +32374,7 @@
         <v>44841</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -32452,7 +32452,7 @@
         <v>46281</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -32530,7 +32530,7 @@
         <v>46281</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -32608,7 +32608,7 @@
         <v>46281</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -32686,7 +32686,7 @@
         <v>45043</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -32764,7 +32764,7 @@
         <v>46281</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -32842,7 +32842,7 @@
         <v>46238</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -32920,7 +32920,7 @@
         <v>46281</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -32998,7 +32998,7 @@
         <v>44984</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -33076,7 +33076,7 @@
         <v>44889</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -33154,7 +33154,7 @@
         <v>44984</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -33232,7 +33232,7 @@
         <v>44841</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -33310,7 +33310,7 @@
         <v>45517</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -33388,7 +33388,7 @@
         <v>45576</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -33466,7 +33466,7 @@
         <v>44966</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -33544,7 +33544,7 @@
         <v>45113</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -33622,7 +33622,7 @@
         <v>46288</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -33700,7 +33700,7 @@
         <v>45073</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -33778,7 +33778,7 @@
         <v>46077</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -33851,7 +33851,7 @@
         <v>44854</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -33929,7 +33929,7 @@
         <v>46289</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -34007,7 +34007,7 @@
         <v>46170</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -34080,7 +34080,7 @@
         <v>46174</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -34158,7 +34158,7 @@
         <v>45323</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -34231,7 +34231,7 @@
         <v>46248</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -34304,7 +34304,7 @@
         <v>46247</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -34377,7 +34377,7 @@
         <v>45028</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -34450,7 +34450,7 @@
         <v>45596</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -34528,7 +34528,7 @@
         <v>46248</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -34601,7 +34601,7 @@
         <v>45664</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -34679,7 +34679,7 @@
         <v>45057</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -34757,7 +34757,7 @@
         <v>45113</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -34835,7 +34835,7 @@
         <v>44477</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -34908,7 +34908,7 @@
         <v>45677</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -34986,7 +34986,7 @@
         <v>45168</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -35064,7 +35064,7 @@
         <v>45090</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -35137,7 +35137,7 @@
         <v>45482</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -35210,7 +35210,7 @@
         <v>45679</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -35288,7 +35288,7 @@
         <v>45534</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -35366,7 +35366,7 @@
         <v>44841</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -35444,7 +35444,7 @@
         <v>45397</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -35522,7 +35522,7 @@
         <v>44589</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -35595,7 +35595,7 @@
         <v>45482</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -35668,7 +35668,7 @@
         <v>45555</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -35746,7 +35746,7 @@
         <v>45490</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -35819,7 +35819,7 @@
         <v>45222</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -35892,7 +35892,7 @@
         <v>45216</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -35970,7 +35970,7 @@
         <v>45093</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -36048,7 +36048,7 @@
         <v>45490</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -36121,7 +36121,7 @@
         <v>45490</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -36194,7 +36194,7 @@
         <v>45490</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -36267,7 +36267,7 @@
         <v>45490</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -36340,7 +36340,7 @@
         <v>45451</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -36418,7 +36418,7 @@
         <v>44823</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -36496,7 +36496,7 @@
         <v>44820</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -36569,7 +36569,7 @@
         <v>45392</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -36642,7 +36642,7 @@
         <v>44823</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -36720,7 +36720,7 @@
         <v>45327</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -36793,7 +36793,7 @@
         <v>45327</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -36866,7 +36866,7 @@
         <v>44824</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -36944,7 +36944,7 @@
         <v>45756</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -37017,7 +37017,7 @@
         <v>45841</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -37095,7 +37095,7 @@
         <v>46147</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -37168,7 +37168,7 @@
         <v>46147</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -37241,7 +37241,7 @@
         <v>46147</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -37314,7 +37314,7 @@
         <v>46148</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -37387,7 +37387,7 @@
         <v>46148</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>

--- a/Översikt JOKKMOKK.xlsx
+++ b/Översikt JOKKMOKK.xlsx
@@ -601,7 +601,7 @@
         <v>45680</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -766,7 +766,7 @@
         <v>45971</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -918,7 +918,7 @@
         <v>46230</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1067,7 +1067,7 @@
         <v>46043</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1205,7 +1205,7 @@
         <v>46184</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1346,7 +1346,7 @@
         <v>46177</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1486,7 +1486,7 @@
         <v>44917</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1624,7 +1624,7 @@
         <v>44539</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1760,7 +1760,7 @@
         <v>46244</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1896,7 +1896,7 @@
         <v>44824</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>45222</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2165,7 +2165,7 @@
         <v>45672</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2297,7 +2297,7 @@
         <v>45805</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2429,7 +2429,7 @@
         <v>46010</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2556,7 +2556,7 @@
         <v>44781</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2683,7 +2683,7 @@
         <v>45476</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2810,7 +2810,7 @@
         <v>45985</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2937,7 +2937,7 @@
         <v>45237</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -3068,7 +3068,7 @@
         <v>45649</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3197,7 +3197,7 @@
         <v>45993</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3321,7 +3321,7 @@
         <v>45484</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3448,7 +3448,7 @@
         <v>44474</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3579,7 +3579,7 @@
         <v>44722</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3702,7 +3702,7 @@
         <v>45174</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3829,7 +3829,7 @@
         <v>45672</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3956,7 +3956,7 @@
         <v>44552</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -4075,7 +4075,7 @@
         <v>45649</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -4199,7 +4199,7 @@
         <v>45994</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4318,7 +4318,7 @@
         <v>45986</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4437,7 +4437,7 @@
         <v>45596</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4560,7 +4560,7 @@
         <v>46184</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4683,7 +4683,7 @@
         <v>45476</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4801,7 +4801,7 @@
         <v>45810</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4918,7 +4918,7 @@
         <v>45113</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -5036,7 +5036,7 @@
         <v>46283</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -5158,7 +5158,7 @@
         <v>46042</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -5279,7 +5279,7 @@
         <v>45940</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5395,7 +5395,7 @@
         <v>46184</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5511,7 +5511,7 @@
         <v>46101</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5626,7 +5626,7 @@
         <v>44722</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5741,7 +5741,7 @@
         <v>46149</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5851,7 +5851,7 @@
         <v>44490</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5965,7 +5965,7 @@
         <v>45484</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -6079,7 +6079,7 @@
         <v>45609</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -6197,7 +6197,7 @@
         <v>46184</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -6311,7 +6311,7 @@
         <v>46090</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6420,7 +6420,7 @@
         <v>46113</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6533,7 +6533,7 @@
         <v>45170</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6646,7 +6646,7 @@
         <v>46206</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6754,7 +6754,7 @@
         <v>46213</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6866,7 +6866,7 @@
         <v>45114</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6979,7 +6979,7 @@
         <v>46013</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -7091,7 +7091,7 @@
         <v>45134</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -7198,7 +7198,7 @@
         <v>45649</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -7314,7 +7314,7 @@
         <v>44545</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -7421,7 +7421,7 @@
         <v>45748</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7528,7 +7528,7 @@
         <v>45012</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7635,7 +7635,7 @@
         <v>44825</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7751,7 +7751,7 @@
         <v>44810</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7861,7 +7861,7 @@
         <v>44726</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7972,7 +7972,7 @@
         <v>44824</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -8083,7 +8083,7 @@
         <v>45891</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -8194,7 +8194,7 @@
         <v>45891</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -8309,7 +8309,7 @@
         <v>45897</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -8420,7 +8420,7 @@
         <v>45951</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8531,7 +8531,7 @@
         <v>45992</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8642,7 +8642,7 @@
         <v>46178</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8753,7 +8753,7 @@
         <v>46184</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8864,7 +8864,7 @@
         <v>45113</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8975,7 +8975,7 @@
         <v>46184</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -9086,7 +9086,7 @@
         <v>46213</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -9197,7 +9197,7 @@
         <v>46184</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -9308,7 +9308,7 @@
         <v>46261</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -9418,7 +9418,7 @@
         <v>45035</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -9529,7 +9529,7 @@
         <v>45225</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9639,7 +9639,7 @@
         <v>45222</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9744,7 +9744,7 @@
         <v>46027</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9849,7 +9849,7 @@
         <v>45799</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9963,7 +9963,7 @@
         <v>45919</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -10073,7 +10073,7 @@
         <v>45572</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -10183,7 +10183,7 @@
         <v>45944</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -10293,7 +10293,7 @@
         <v>45951</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -10403,7 +10403,7 @@
         <v>45958</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -10513,7 +10513,7 @@
         <v>45974</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -10623,7 +10623,7 @@
         <v>45974</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10733,7 +10733,7 @@
         <v>44545</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10838,7 +10838,7 @@
         <v>45982</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10952,7 +10952,7 @@
         <v>45985</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -11062,7 +11062,7 @@
         <v>46137</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -11172,7 +11172,7 @@
         <v>45819</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -11282,7 +11282,7 @@
         <v>45672</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -11392,7 +11392,7 @@
         <v>45826</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -11502,7 +11502,7 @@
         <v>44865</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -11616,7 +11616,7 @@
         <v>45838</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11726,7 +11726,7 @@
         <v>45608</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11836,7 +11836,7 @@
         <v>45600</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11941,7 +11941,7 @@
         <v>45876</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -12051,7 +12051,7 @@
         <v>46197</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -12161,7 +12161,7 @@
         <v>46199</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -12271,7 +12271,7 @@
         <v>46199</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -12381,7 +12381,7 @@
         <v>45915</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -12491,7 +12491,7 @@
         <v>46276</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -12601,7 +12601,7 @@
         <v>46240</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -12711,7 +12711,7 @@
         <v>45918</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -12816,7 +12816,7 @@
         <v>46272</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -12926,7 +12926,7 @@
         <v>44967</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -13036,7 +13036,7 @@
         <v>45358</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -13141,7 +13141,7 @@
         <v>44820</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -13219,7 +13219,7 @@
         <v>44676</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -13292,7 +13292,7 @@
         <v>44543</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -13370,7 +13370,7 @@
         <v>44543</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -13448,7 +13448,7 @@
         <v>44543</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -13521,7 +13521,7 @@
         <v>44586</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -13599,7 +13599,7 @@
         <v>44586</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -13677,7 +13677,7 @@
         <v>44663</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -13750,7 +13750,7 @@
         <v>44685</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -13828,7 +13828,7 @@
         <v>44539</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -13906,7 +13906,7 @@
         <v>44543</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -13984,7 +13984,7 @@
         <v>44543</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -14062,7 +14062,7 @@
         <v>44638</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -14140,7 +14140,7 @@
         <v>44743</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -14218,7 +14218,7 @@
         <v>44543</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -14296,7 +14296,7 @@
         <v>44586</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -14374,7 +14374,7 @@
         <v>44573</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -14452,7 +14452,7 @@
         <v>44820</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -14530,7 +14530,7 @@
         <v>44824</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -14608,7 +14608,7 @@
         <v>44532</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -14681,7 +14681,7 @@
         <v>44868</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -14759,7 +14759,7 @@
         <v>45086</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -14832,7 +14832,7 @@
         <v>44862</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -14905,7 +14905,7 @@
         <v>44841</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -14983,7 +14983,7 @@
         <v>44873</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -15061,7 +15061,7 @@
         <v>45113</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -15139,7 +15139,7 @@
         <v>44866</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -15217,7 +15217,7 @@
         <v>45106</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -15295,7 +15295,7 @@
         <v>44868</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -15368,7 +15368,7 @@
         <v>45474</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -15446,7 +15446,7 @@
         <v>45474</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -15524,7 +15524,7 @@
         <v>45474</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -15602,7 +15602,7 @@
         <v>45474</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -15680,7 +15680,7 @@
         <v>45474</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -15758,7 +15758,7 @@
         <v>45471</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -15836,7 +15836,7 @@
         <v>45463</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -15914,7 +15914,7 @@
         <v>45572</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -15992,7 +15992,7 @@
         <v>46021</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -16065,7 +16065,7 @@
         <v>46010</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -16138,7 +16138,7 @@
         <v>46010</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -16216,7 +16216,7 @@
         <v>46009</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -16289,7 +16289,7 @@
         <v>44966</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -16362,7 +16362,7 @@
         <v>45884</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -16440,7 +16440,7 @@
         <v>46030</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -16518,7 +16518,7 @@
         <v>45505</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -16596,7 +16596,7 @@
         <v>45994</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -16674,7 +16674,7 @@
         <v>45883</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -16752,7 +16752,7 @@
         <v>45992</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -16830,7 +16830,7 @@
         <v>45993</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -16908,7 +16908,7 @@
         <v>44477</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -16981,7 +16981,7 @@
         <v>44841</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -17059,7 +17059,7 @@
         <v>44984</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -17137,7 +17137,7 @@
         <v>45693</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -17210,7 +17210,7 @@
         <v>45544</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -17288,7 +17288,7 @@
         <v>45897</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -17366,7 +17366,7 @@
         <v>45073</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -17444,7 +17444,7 @@
         <v>45901</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -17522,7 +17522,7 @@
         <v>45904</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -17600,7 +17600,7 @@
         <v>45491</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -17673,7 +17673,7 @@
         <v>45883</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -17751,7 +17751,7 @@
         <v>45646</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -17824,7 +17824,7 @@
         <v>45907</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -17897,7 +17897,7 @@
         <v>45259</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -17975,7 +17975,7 @@
         <v>45572</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -18053,7 +18053,7 @@
         <v>45912</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -18131,7 +18131,7 @@
         <v>45558</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -18209,7 +18209,7 @@
         <v>45664</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -18287,7 +18287,7 @@
         <v>45491</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -18360,7 +18360,7 @@
         <v>45918</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -18438,7 +18438,7 @@
         <v>45572</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -18516,7 +18516,7 @@
         <v>45028</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -18589,7 +18589,7 @@
         <v>45596</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -18667,7 +18667,7 @@
         <v>46077</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -18745,7 +18745,7 @@
         <v>46077</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -18823,7 +18823,7 @@
         <v>46077</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -18901,7 +18901,7 @@
         <v>46077</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -18979,7 +18979,7 @@
         <v>45928</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -19057,7 +19057,7 @@
         <v>45887</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -19135,7 +19135,7 @@
         <v>44984</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -19213,7 +19213,7 @@
         <v>44984</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -19291,7 +19291,7 @@
         <v>45544</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -19369,7 +19369,7 @@
         <v>45532</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -19442,7 +19442,7 @@
         <v>44984</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -19515,7 +19515,7 @@
         <v>44984</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -19588,7 +19588,7 @@
         <v>45526</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -19661,7 +19661,7 @@
         <v>45586</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -19734,7 +19734,7 @@
         <v>46092</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -19812,7 +19812,7 @@
         <v>46092</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -19890,7 +19890,7 @@
         <v>46092</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -19968,7 +19968,7 @@
         <v>46092</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -20046,7 +20046,7 @@
         <v>45940</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -20124,7 +20124,7 @@
         <v>45943</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -20202,7 +20202,7 @@
         <v>45942</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -20280,7 +20280,7 @@
         <v>45942</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -20358,7 +20358,7 @@
         <v>45946</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -20436,7 +20436,7 @@
         <v>45590</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -20514,7 +20514,7 @@
         <v>45950</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -20587,7 +20587,7 @@
         <v>45596</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -20665,7 +20665,7 @@
         <v>45950</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -20738,7 +20738,7 @@
         <v>45951</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -20816,7 +20816,7 @@
         <v>45951</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -20894,7 +20894,7 @@
         <v>45951</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -20972,7 +20972,7 @@
         <v>45951</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -21050,7 +21050,7 @@
         <v>44984</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -21128,7 +21128,7 @@
         <v>45951</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -21206,7 +21206,7 @@
         <v>45951</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -21284,7 +21284,7 @@
         <v>45951</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -21362,7 +21362,7 @@
         <v>46106</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -21440,7 +21440,7 @@
         <v>46106</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -21518,7 +21518,7 @@
         <v>46106</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -21596,7 +21596,7 @@
         <v>45953</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -21674,7 +21674,7 @@
         <v>45953</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -21752,7 +21752,7 @@
         <v>45953</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -21830,7 +21830,7 @@
         <v>46108</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -21908,7 +21908,7 @@
         <v>46108</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -21986,7 +21986,7 @@
         <v>45953</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -22064,7 +22064,7 @@
         <v>46108</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -22142,7 +22142,7 @@
         <v>46113</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -22220,7 +22220,7 @@
         <v>46113</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -22298,7 +22298,7 @@
         <v>46113</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -22376,7 +22376,7 @@
         <v>46113</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -22454,7 +22454,7 @@
         <v>46113</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -22532,7 +22532,7 @@
         <v>46113</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -22610,7 +22610,7 @@
         <v>46114</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -22688,7 +22688,7 @@
         <v>45993</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -22766,7 +22766,7 @@
         <v>45960</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -22839,7 +22839,7 @@
         <v>45572</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -22917,7 +22917,7 @@
         <v>45964</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -22995,7 +22995,7 @@
         <v>45965</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -23073,7 +23073,7 @@
         <v>45565</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -23151,7 +23151,7 @@
         <v>45965</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -23229,7 +23229,7 @@
         <v>45968</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -23302,7 +23302,7 @@
         <v>45967</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -23375,7 +23375,7 @@
         <v>45813</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -23448,7 +23448,7 @@
         <v>45972</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -23526,7 +23526,7 @@
         <v>45971</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -23604,7 +23604,7 @@
         <v>44477</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -23677,7 +23677,7 @@
         <v>45974</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -23755,7 +23755,7 @@
         <v>45973</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -23833,7 +23833,7 @@
         <v>45974</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -23911,7 +23911,7 @@
         <v>45973</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -23989,7 +23989,7 @@
         <v>45974</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -24067,7 +24067,7 @@
         <v>45974</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -24145,7 +24145,7 @@
         <v>45974</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -24223,7 +24223,7 @@
         <v>45111</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -24296,7 +24296,7 @@
         <v>45974</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -24374,7 +24374,7 @@
         <v>45975</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -24447,7 +24447,7 @@
         <v>45975</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -24525,7 +24525,7 @@
         <v>46010</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -24598,7 +24598,7 @@
         <v>45979</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -24676,7 +24676,7 @@
         <v>45979</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -24754,7 +24754,7 @@
         <v>44802</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -24827,7 +24827,7 @@
         <v>45985</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -24905,7 +24905,7 @@
         <v>45590</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -24983,7 +24983,7 @@
         <v>45985</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -25061,7 +25061,7 @@
         <v>45973</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -25139,7 +25139,7 @@
         <v>45721</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -25212,7 +25212,7 @@
         <v>45994</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -25290,7 +25290,7 @@
         <v>45995</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -25368,7 +25368,7 @@
         <v>45995</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -25446,7 +25446,7 @@
         <v>45124</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -25524,7 +25524,7 @@
         <v>45488</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -25597,7 +25597,7 @@
         <v>45953</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -25675,7 +25675,7 @@
         <v>46006</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -25748,7 +25748,7 @@
         <v>46137</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -25826,7 +25826,7 @@
         <v>45028</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -25899,7 +25899,7 @@
         <v>45819</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -25977,7 +25977,7 @@
         <v>46010</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -26050,7 +26050,7 @@
         <v>45824</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -26123,7 +26123,7 @@
         <v>45826</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -26201,7 +26201,7 @@
         <v>45904</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -26274,7 +26274,7 @@
         <v>45827</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -26352,7 +26352,7 @@
         <v>45516</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -26430,7 +26430,7 @@
         <v>45022</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -26508,7 +26508,7 @@
         <v>45608</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -26581,7 +26581,7 @@
         <v>45903</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -26659,7 +26659,7 @@
         <v>46083</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -26732,7 +26732,7 @@
         <v>45842</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -26810,7 +26810,7 @@
         <v>45838</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -26888,7 +26888,7 @@
         <v>45474</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -26966,7 +26966,7 @@
         <v>46162</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -27044,7 +27044,7 @@
         <v>46164</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -27122,7 +27122,7 @@
         <v>45860</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -27195,7 +27195,7 @@
         <v>45824</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -27268,7 +27268,7 @@
         <v>45883</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -27346,7 +27346,7 @@
         <v>45078</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -27424,7 +27424,7 @@
         <v>44493</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -27502,7 +27502,7 @@
         <v>46170</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -27580,7 +27580,7 @@
         <v>46170</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -27653,7 +27653,7 @@
         <v>45807</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -27731,7 +27731,7 @@
         <v>45868</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -27804,7 +27804,7 @@
         <v>45124</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -27882,7 +27882,7 @@
         <v>46177</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -27960,7 +27960,7 @@
         <v>46177</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -28038,7 +28038,7 @@
         <v>46177</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -28116,7 +28116,7 @@
         <v>46177</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -28194,7 +28194,7 @@
         <v>46178</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -28272,7 +28272,7 @@
         <v>46183</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -28350,7 +28350,7 @@
         <v>44539</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -28428,7 +28428,7 @@
         <v>46185</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -28506,7 +28506,7 @@
         <v>45166</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -28579,7 +28579,7 @@
         <v>44984</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -28657,7 +28657,7 @@
         <v>44984</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -28735,7 +28735,7 @@
         <v>44984</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -28813,7 +28813,7 @@
         <v>44984</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -28886,7 +28886,7 @@
         <v>44984</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -28964,7 +28964,7 @@
         <v>46191</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -29042,7 +29042,7 @@
         <v>45124</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -29120,7 +29120,7 @@
         <v>46192</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -29198,7 +29198,7 @@
         <v>46191</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -29276,7 +29276,7 @@
         <v>45613</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -29349,7 +29349,7 @@
         <v>45678</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -29427,7 +29427,7 @@
         <v>46197</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -29505,7 +29505,7 @@
         <v>46197</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -29583,7 +29583,7 @@
         <v>45565</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -29656,7 +29656,7 @@
         <v>45880</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -29734,7 +29734,7 @@
         <v>46197</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -29812,7 +29812,7 @@
         <v>45986</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -29885,7 +29885,7 @@
         <v>46199</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -29963,7 +29963,7 @@
         <v>46199</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -30041,7 +30041,7 @@
         <v>46199</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -30119,7 +30119,7 @@
         <v>45224</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -30197,7 +30197,7 @@
         <v>46198</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -30270,7 +30270,7 @@
         <v>45555</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -30343,7 +30343,7 @@
         <v>45349</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -30416,7 +30416,7 @@
         <v>46205</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -30489,7 +30489,7 @@
         <v>46204</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -30567,7 +30567,7 @@
         <v>46205</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -30640,7 +30640,7 @@
         <v>46206</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -30713,7 +30713,7 @@
         <v>46206</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -30786,7 +30786,7 @@
         <v>46211</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -30864,7 +30864,7 @@
         <v>45604</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -30942,7 +30942,7 @@
         <v>46254</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -31020,7 +31020,7 @@
         <v>46215</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -31093,7 +31093,7 @@
         <v>46215</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -31166,7 +31166,7 @@
         <v>46255</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -31239,7 +31239,7 @@
         <v>46212</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -31317,7 +31317,7 @@
         <v>46253</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -31390,7 +31390,7 @@
         <v>46212</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -31468,7 +31468,7 @@
         <v>45520</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -31546,7 +31546,7 @@
         <v>46216</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -31619,7 +31619,7 @@
         <v>46175</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -31692,7 +31692,7 @@
         <v>46216</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -31765,7 +31765,7 @@
         <v>44851</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -31838,7 +31838,7 @@
         <v>46266</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -31916,7 +31916,7 @@
         <v>45257</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -31994,7 +31994,7 @@
         <v>45474</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -32072,7 +32072,7 @@
         <v>45763</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -32150,7 +32150,7 @@
         <v>46274</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -32228,7 +32228,7 @@
         <v>46009</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -32301,7 +32301,7 @@
         <v>46237</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -32374,7 +32374,7 @@
         <v>44841</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -32452,7 +32452,7 @@
         <v>46281</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -32530,7 +32530,7 @@
         <v>46281</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -32608,7 +32608,7 @@
         <v>46281</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -32686,7 +32686,7 @@
         <v>45043</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -32764,7 +32764,7 @@
         <v>46281</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -32842,7 +32842,7 @@
         <v>46238</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -32920,7 +32920,7 @@
         <v>46281</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -32998,7 +32998,7 @@
         <v>44984</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -33076,7 +33076,7 @@
         <v>44889</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -33154,7 +33154,7 @@
         <v>44984</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -33232,7 +33232,7 @@
         <v>44841</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -33310,7 +33310,7 @@
         <v>45517</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -33388,7 +33388,7 @@
         <v>45576</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -33466,7 +33466,7 @@
         <v>44966</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -33544,7 +33544,7 @@
         <v>45113</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -33622,7 +33622,7 @@
         <v>46288</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -33700,7 +33700,7 @@
         <v>45073</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -33778,7 +33778,7 @@
         <v>46077</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -33851,7 +33851,7 @@
         <v>44854</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -33929,7 +33929,7 @@
         <v>46289</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -34007,7 +34007,7 @@
         <v>46170</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -34080,7 +34080,7 @@
         <v>46174</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -34158,7 +34158,7 @@
         <v>45323</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -34231,7 +34231,7 @@
         <v>46248</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -34304,7 +34304,7 @@
         <v>46247</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -34377,7 +34377,7 @@
         <v>45028</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -34450,7 +34450,7 @@
         <v>45596</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -34528,7 +34528,7 @@
         <v>46248</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -34601,7 +34601,7 @@
         <v>45664</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -34679,7 +34679,7 @@
         <v>45057</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -34757,7 +34757,7 @@
         <v>45113</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -34835,7 +34835,7 @@
         <v>44477</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -34908,7 +34908,7 @@
         <v>45677</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -34986,7 +34986,7 @@
         <v>45168</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -35064,7 +35064,7 @@
         <v>45090</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -35137,7 +35137,7 @@
         <v>45482</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -35210,7 +35210,7 @@
         <v>45679</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -35288,7 +35288,7 @@
         <v>45534</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -35366,7 +35366,7 @@
         <v>44841</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -35444,7 +35444,7 @@
         <v>45397</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -35522,7 +35522,7 @@
         <v>44589</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -35595,7 +35595,7 @@
         <v>45482</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -35668,7 +35668,7 @@
         <v>45555</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -35746,7 +35746,7 @@
         <v>45490</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -35819,7 +35819,7 @@
         <v>45222</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -35892,7 +35892,7 @@
         <v>45216</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -35970,7 +35970,7 @@
         <v>45093</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -36048,7 +36048,7 @@
         <v>45490</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -36121,7 +36121,7 @@
         <v>45490</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -36194,7 +36194,7 @@
         <v>45490</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -36267,7 +36267,7 @@
         <v>45490</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -36340,7 +36340,7 @@
         <v>45451</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -36418,7 +36418,7 @@
         <v>44823</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -36496,7 +36496,7 @@
         <v>44820</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -36569,7 +36569,7 @@
         <v>45392</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -36642,7 +36642,7 @@
         <v>44823</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -36720,7 +36720,7 @@
         <v>45327</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -36793,7 +36793,7 @@
         <v>45327</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -36866,7 +36866,7 @@
         <v>44824</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -36944,7 +36944,7 @@
         <v>45756</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -37017,7 +37017,7 @@
         <v>45841</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -37095,7 +37095,7 @@
         <v>46147</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -37168,7 +37168,7 @@
         <v>46147</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -37241,7 +37241,7 @@
         <v>46147</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -37314,7 +37314,7 @@
         <v>46148</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -37387,7 +37387,7 @@
         <v>46148</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>

--- a/Översikt JOKKMOKK.xlsx
+++ b/Översikt JOKKMOKK.xlsx
@@ -601,7 +601,7 @@
         <v>45680</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -766,7 +766,7 @@
         <v>45971</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -918,7 +918,7 @@
         <v>46230</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1067,7 +1067,7 @@
         <v>46043</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1205,7 +1205,7 @@
         <v>46184</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1346,7 +1346,7 @@
         <v>46177</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1486,7 +1486,7 @@
         <v>44917</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1624,7 +1624,7 @@
         <v>44539</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1760,7 +1760,7 @@
         <v>46244</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1896,7 +1896,7 @@
         <v>44824</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>45222</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2165,7 +2165,7 @@
         <v>45672</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2297,7 +2297,7 @@
         <v>44781</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2424,7 +2424,7 @@
         <v>45805</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2556,7 +2556,7 @@
         <v>46010</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2683,7 +2683,7 @@
         <v>45476</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2810,7 +2810,7 @@
         <v>45985</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2937,7 +2937,7 @@
         <v>45237</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -3068,7 +3068,7 @@
         <v>45649</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3197,7 +3197,7 @@
         <v>45993</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3321,7 +3321,7 @@
         <v>44474</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3452,7 +3452,7 @@
         <v>45484</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3579,7 +3579,7 @@
         <v>44722</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3702,7 +3702,7 @@
         <v>45174</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3829,7 +3829,7 @@
         <v>45672</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3956,7 +3956,7 @@
         <v>45649</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -4080,7 +4080,7 @@
         <v>44552</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -4199,7 +4199,7 @@
         <v>45986</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4318,7 +4318,7 @@
         <v>45994</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4437,7 +4437,7 @@
         <v>45596</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4560,7 +4560,7 @@
         <v>46184</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4683,7 +4683,7 @@
         <v>45476</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4801,7 +4801,7 @@
         <v>45810</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4918,7 +4918,7 @@
         <v>45113</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -5036,7 +5036,7 @@
         <v>46283</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -5158,7 +5158,7 @@
         <v>46042</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -5279,7 +5279,7 @@
         <v>45940</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5395,7 +5395,7 @@
         <v>46184</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5511,7 +5511,7 @@
         <v>46101</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5626,7 +5626,7 @@
         <v>46149</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5736,7 +5736,7 @@
         <v>44722</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5851,7 +5851,7 @@
         <v>45484</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5965,7 +5965,7 @@
         <v>44490</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -6079,7 +6079,7 @@
         <v>45609</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -6197,7 +6197,7 @@
         <v>46184</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -6311,7 +6311,7 @@
         <v>46090</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6420,7 +6420,7 @@
         <v>45114</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6533,7 +6533,7 @@
         <v>45170</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6646,7 +6646,7 @@
         <v>46113</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6759,7 +6759,7 @@
         <v>46206</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6867,7 +6867,7 @@
         <v>46213</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6979,7 +6979,7 @@
         <v>45748</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -7086,7 +7086,7 @@
         <v>45134</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -7193,7 +7193,7 @@
         <v>46013</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -7305,7 +7305,7 @@
         <v>45649</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -7421,7 +7421,7 @@
         <v>44545</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7528,7 +7528,7 @@
         <v>45012</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7635,7 +7635,7 @@
         <v>44825</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7751,7 +7751,7 @@
         <v>44810</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7861,7 +7861,7 @@
         <v>44726</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7972,7 +7972,7 @@
         <v>44824</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -8083,7 +8083,7 @@
         <v>45891</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -8194,7 +8194,7 @@
         <v>45891</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -8309,7 +8309,7 @@
         <v>45897</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -8420,7 +8420,7 @@
         <v>45951</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8531,7 +8531,7 @@
         <v>45992</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8642,7 +8642,7 @@
         <v>46178</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8753,7 +8753,7 @@
         <v>45113</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8864,7 +8864,7 @@
         <v>46184</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8975,7 +8975,7 @@
         <v>46184</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -9086,7 +9086,7 @@
         <v>46213</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -9197,7 +9197,7 @@
         <v>46184</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -9308,7 +9308,7 @@
         <v>46261</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -9418,7 +9418,7 @@
         <v>45035</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -9529,7 +9529,7 @@
         <v>46027</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9634,7 +9634,7 @@
         <v>45799</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9748,7 +9748,7 @@
         <v>45919</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9858,7 +9858,7 @@
         <v>45572</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9968,7 +9968,7 @@
         <v>45944</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -10078,7 +10078,7 @@
         <v>45951</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -10188,7 +10188,7 @@
         <v>45958</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -10298,7 +10298,7 @@
         <v>44545</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -10403,7 +10403,7 @@
         <v>45974</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -10513,7 +10513,7 @@
         <v>45974</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -10623,7 +10623,7 @@
         <v>45819</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10733,7 +10733,7 @@
         <v>45982</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10847,7 +10847,7 @@
         <v>45985</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10957,7 +10957,7 @@
         <v>45826</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -11067,7 +11067,7 @@
         <v>45838</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -11177,7 +11177,7 @@
         <v>46137</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -11287,7 +11287,7 @@
         <v>45225</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -11397,7 +11397,7 @@
         <v>45672</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -11507,7 +11507,7 @@
         <v>45876</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -11617,7 +11617,7 @@
         <v>45608</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11727,7 +11727,7 @@
         <v>45600</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11832,7 +11832,7 @@
         <v>46197</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11942,7 +11942,7 @@
         <v>46199</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -12052,7 +12052,7 @@
         <v>46199</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -12162,7 +12162,7 @@
         <v>45915</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -12272,7 +12272,7 @@
         <v>46276</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -12382,7 +12382,7 @@
         <v>45222</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -12487,7 +12487,7 @@
         <v>46240</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -12597,7 +12597,7 @@
         <v>44865</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -12711,7 +12711,7 @@
         <v>45918</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -12816,7 +12816,7 @@
         <v>46272</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -12926,7 +12926,7 @@
         <v>44967</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -13036,7 +13036,7 @@
         <v>45358</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -13141,7 +13141,7 @@
         <v>44820</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -13219,7 +13219,7 @@
         <v>44676</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -13292,7 +13292,7 @@
         <v>44543</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -13370,7 +13370,7 @@
         <v>44543</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -13448,7 +13448,7 @@
         <v>44543</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -13521,7 +13521,7 @@
         <v>44586</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -13599,7 +13599,7 @@
         <v>44586</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -13677,7 +13677,7 @@
         <v>44663</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -13750,7 +13750,7 @@
         <v>44685</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -13828,7 +13828,7 @@
         <v>44539</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -13906,7 +13906,7 @@
         <v>44543</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -13984,7 +13984,7 @@
         <v>44543</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -14062,7 +14062,7 @@
         <v>44638</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -14140,7 +14140,7 @@
         <v>44743</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -14218,7 +14218,7 @@
         <v>44543</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -14296,7 +14296,7 @@
         <v>44586</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -14374,7 +14374,7 @@
         <v>44573</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -14452,7 +14452,7 @@
         <v>44820</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -14530,7 +14530,7 @@
         <v>44824</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -14608,7 +14608,7 @@
         <v>44532</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -14681,7 +14681,7 @@
         <v>44868</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -14759,7 +14759,7 @@
         <v>45028</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -14832,7 +14832,7 @@
         <v>44966</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -14905,7 +14905,7 @@
         <v>45106</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -14983,7 +14983,7 @@
         <v>44841</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -15061,7 +15061,7 @@
         <v>45884</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -15139,7 +15139,7 @@
         <v>44539</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -15217,7 +15217,7 @@
         <v>45451</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -15295,7 +15295,7 @@
         <v>45596</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -15373,7 +15373,7 @@
         <v>46006</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -15446,7 +15446,7 @@
         <v>45491</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -15519,7 +15519,7 @@
         <v>45586</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -15592,7 +15592,7 @@
         <v>46010</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -15665,7 +15665,7 @@
         <v>45482</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -15738,7 +15738,7 @@
         <v>45463</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -15816,7 +15816,7 @@
         <v>45222</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -15889,7 +15889,7 @@
         <v>45572</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -15967,7 +15967,7 @@
         <v>46021</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -16040,7 +16040,7 @@
         <v>45558</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -16118,7 +16118,7 @@
         <v>46010</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -16191,7 +16191,7 @@
         <v>46010</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -16269,7 +16269,7 @@
         <v>46009</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -16342,7 +16342,7 @@
         <v>45897</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -16420,7 +16420,7 @@
         <v>45993</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -16498,7 +16498,7 @@
         <v>45992</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -16576,7 +16576,7 @@
         <v>45994</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -16654,7 +16654,7 @@
         <v>46030</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -16732,7 +16732,7 @@
         <v>45901</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -16810,7 +16810,7 @@
         <v>45086</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -16883,7 +16883,7 @@
         <v>45482</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -16956,7 +16956,7 @@
         <v>45693</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -17029,7 +17029,7 @@
         <v>45677</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -17107,7 +17107,7 @@
         <v>45904</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -17185,7 +17185,7 @@
         <v>45907</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -17258,7 +17258,7 @@
         <v>45544</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -17336,7 +17336,7 @@
         <v>45912</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -17414,7 +17414,7 @@
         <v>45918</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -17492,7 +17492,7 @@
         <v>45572</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -17570,7 +17570,7 @@
         <v>44984</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -17643,7 +17643,7 @@
         <v>44984</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -17716,7 +17716,7 @@
         <v>45544</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -17794,7 +17794,7 @@
         <v>45259</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -17872,7 +17872,7 @@
         <v>45596</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -17950,7 +17950,7 @@
         <v>45883</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -18028,7 +18028,7 @@
         <v>45349</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -18101,7 +18101,7 @@
         <v>45532</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -18174,7 +18174,7 @@
         <v>45124</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -18252,7 +18252,7 @@
         <v>45572</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -18330,7 +18330,7 @@
         <v>45887</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -18408,7 +18408,7 @@
         <v>45928</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -18486,7 +18486,7 @@
         <v>44984</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -18564,7 +18564,7 @@
         <v>44984</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -18642,7 +18642,7 @@
         <v>44984</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -18720,7 +18720,7 @@
         <v>45664</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -18798,7 +18798,7 @@
         <v>45942</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -18876,7 +18876,7 @@
         <v>45942</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -18954,7 +18954,7 @@
         <v>45943</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -19032,7 +19032,7 @@
         <v>45940</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -19110,7 +19110,7 @@
         <v>46077</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -19188,7 +19188,7 @@
         <v>46077</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -19266,7 +19266,7 @@
         <v>46077</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -19344,7 +19344,7 @@
         <v>45679</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -19422,7 +19422,7 @@
         <v>45946</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -19500,7 +19500,7 @@
         <v>46077</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -19578,7 +19578,7 @@
         <v>44873</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -19656,7 +19656,7 @@
         <v>45951</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -19734,7 +19734,7 @@
         <v>45951</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -19812,7 +19812,7 @@
         <v>45951</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -19890,7 +19890,7 @@
         <v>45951</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -19968,7 +19968,7 @@
         <v>45951</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -20046,7 +20046,7 @@
         <v>45951</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -20124,7 +20124,7 @@
         <v>45951</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -20202,7 +20202,7 @@
         <v>45950</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -20275,7 +20275,7 @@
         <v>45950</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -20348,7 +20348,7 @@
         <v>45953</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -20426,7 +20426,7 @@
         <v>44862</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -20499,7 +20499,7 @@
         <v>44984</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -20577,7 +20577,7 @@
         <v>45953</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -20655,7 +20655,7 @@
         <v>45953</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -20733,7 +20733,7 @@
         <v>45953</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -20811,7 +20811,7 @@
         <v>45257</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -20889,7 +20889,7 @@
         <v>45488</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -20962,7 +20962,7 @@
         <v>45323</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -21035,7 +21035,7 @@
         <v>45813</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -21108,7 +21108,7 @@
         <v>45960</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -21181,7 +21181,7 @@
         <v>46092</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -21259,7 +21259,7 @@
         <v>46092</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -21337,7 +21337,7 @@
         <v>46092</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -21415,7 +21415,7 @@
         <v>46092</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -21493,7 +21493,7 @@
         <v>45965</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -21571,7 +21571,7 @@
         <v>45964</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -21649,7 +21649,7 @@
         <v>45124</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -21727,7 +21727,7 @@
         <v>45965</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -21805,7 +21805,7 @@
         <v>45967</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -21878,7 +21878,7 @@
         <v>45646</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -21951,7 +21951,7 @@
         <v>45971</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -22029,7 +22029,7 @@
         <v>45043</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -22107,7 +22107,7 @@
         <v>45968</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -22180,7 +22180,7 @@
         <v>45973</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -22258,7 +22258,7 @@
         <v>45973</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -22336,7 +22336,7 @@
         <v>45516</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -22414,7 +22414,7 @@
         <v>45972</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -22492,7 +22492,7 @@
         <v>45975</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -22570,7 +22570,7 @@
         <v>45974</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -22648,7 +22648,7 @@
         <v>45974</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -22726,7 +22726,7 @@
         <v>45974</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -22804,7 +22804,7 @@
         <v>45974</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -22882,7 +22882,7 @@
         <v>45974</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -22960,7 +22960,7 @@
         <v>45975</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -23033,7 +23033,7 @@
         <v>45974</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -23111,7 +23111,7 @@
         <v>46106</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -23189,7 +23189,7 @@
         <v>46106</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -23267,7 +23267,7 @@
         <v>45979</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -23345,7 +23345,7 @@
         <v>45979</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -23423,7 +23423,7 @@
         <v>45590</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -23501,7 +23501,7 @@
         <v>45517</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -23579,7 +23579,7 @@
         <v>46108</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -23657,7 +23657,7 @@
         <v>45819</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -23735,7 +23735,7 @@
         <v>46108</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -23813,7 +23813,7 @@
         <v>46108</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -23891,7 +23891,7 @@
         <v>46106</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -23969,7 +23969,7 @@
         <v>45985</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -24047,7 +24047,7 @@
         <v>45985</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -24125,7 +24125,7 @@
         <v>46113</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -24203,7 +24203,7 @@
         <v>45721</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -24276,7 +24276,7 @@
         <v>44889</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -24354,7 +24354,7 @@
         <v>46113</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -24432,7 +24432,7 @@
         <v>46113</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -24510,7 +24510,7 @@
         <v>46114</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -24588,7 +24588,7 @@
         <v>46113</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -24666,7 +24666,7 @@
         <v>46113</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -24744,7 +24744,7 @@
         <v>46113</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -24822,7 +24822,7 @@
         <v>45596</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -24900,7 +24900,7 @@
         <v>44841</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -24978,7 +24978,7 @@
         <v>45824</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -25051,7 +25051,7 @@
         <v>45973</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -25129,7 +25129,7 @@
         <v>45993</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -25207,7 +25207,7 @@
         <v>45572</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -25285,7 +25285,7 @@
         <v>44966</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -25363,7 +25363,7 @@
         <v>45995</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -25441,7 +25441,7 @@
         <v>45995</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -25519,7 +25519,7 @@
         <v>45994</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -25597,7 +25597,7 @@
         <v>45827</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -25675,7 +25675,7 @@
         <v>45826</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -25753,7 +25753,7 @@
         <v>46010</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -25826,7 +25826,7 @@
         <v>45953</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -25904,7 +25904,7 @@
         <v>45474</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -25982,7 +25982,7 @@
         <v>45474</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -26060,7 +26060,7 @@
         <v>45474</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -26138,7 +26138,7 @@
         <v>45838</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -26216,7 +26216,7 @@
         <v>45491</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -26289,7 +26289,7 @@
         <v>44493</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -26367,7 +26367,7 @@
         <v>45216</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -26445,7 +26445,7 @@
         <v>45028</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -26518,7 +26518,7 @@
         <v>46137</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -26596,7 +26596,7 @@
         <v>45904</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -26669,7 +26669,7 @@
         <v>44984</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -26747,7 +26747,7 @@
         <v>44589</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -26820,7 +26820,7 @@
         <v>45868</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -26893,7 +26893,7 @@
         <v>45807</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -26971,7 +26971,7 @@
         <v>45168</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -27049,7 +27049,7 @@
         <v>45111</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -27122,7 +27122,7 @@
         <v>45166</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -27195,7 +27195,7 @@
         <v>45608</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -27268,7 +27268,7 @@
         <v>44477</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -27341,7 +27341,7 @@
         <v>46083</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -27414,7 +27414,7 @@
         <v>45903</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -27492,7 +27492,7 @@
         <v>45842</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -27570,7 +27570,7 @@
         <v>45073</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -27648,7 +27648,7 @@
         <v>45824</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -27721,7 +27721,7 @@
         <v>46162</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -27799,7 +27799,7 @@
         <v>45113</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -27877,7 +27877,7 @@
         <v>46164</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -27955,7 +27955,7 @@
         <v>45860</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -28028,7 +28028,7 @@
         <v>45883</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -28106,7 +28106,7 @@
         <v>45880</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -28184,7 +28184,7 @@
         <v>46170</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -28262,7 +28262,7 @@
         <v>46170</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -28335,7 +28335,7 @@
         <v>45474</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -28413,7 +28413,7 @@
         <v>45474</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -28491,7 +28491,7 @@
         <v>45397</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -28569,7 +28569,7 @@
         <v>45883</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -28647,7 +28647,7 @@
         <v>44868</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -28720,7 +28720,7 @@
         <v>46177</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -28798,7 +28798,7 @@
         <v>46177</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -28876,7 +28876,7 @@
         <v>46178</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -28954,7 +28954,7 @@
         <v>46177</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -29032,7 +29032,7 @@
         <v>46177</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -29110,7 +29110,7 @@
         <v>46183</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -29188,7 +29188,7 @@
         <v>44477</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -29261,7 +29261,7 @@
         <v>46185</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -29339,7 +29339,7 @@
         <v>45604</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -29417,7 +29417,7 @@
         <v>46191</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -29495,7 +29495,7 @@
         <v>46191</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -29573,7 +29573,7 @@
         <v>46192</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -29651,7 +29651,7 @@
         <v>45678</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -29729,7 +29729,7 @@
         <v>45090</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -29802,7 +29802,7 @@
         <v>46198</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -29875,7 +29875,7 @@
         <v>45986</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -29948,7 +29948,7 @@
         <v>45474</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -30026,7 +30026,7 @@
         <v>45613</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -30099,7 +30099,7 @@
         <v>45526</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -30172,7 +30172,7 @@
         <v>46197</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -30250,7 +30250,7 @@
         <v>46197</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -30328,7 +30328,7 @@
         <v>46197</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -30406,7 +30406,7 @@
         <v>46199</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -30484,7 +30484,7 @@
         <v>46199</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -30562,7 +30562,7 @@
         <v>44802</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -30635,7 +30635,7 @@
         <v>46199</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -30713,7 +30713,7 @@
         <v>44851</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -30786,7 +30786,7 @@
         <v>45534</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -30864,7 +30864,7 @@
         <v>46204</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -30942,7 +30942,7 @@
         <v>46205</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -31015,7 +31015,7 @@
         <v>46206</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -31088,7 +31088,7 @@
         <v>46206</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -31161,7 +31161,7 @@
         <v>46205</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -31234,7 +31234,7 @@
         <v>46212</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -31312,7 +31312,7 @@
         <v>46211</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -31390,7 +31390,7 @@
         <v>46212</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -31468,7 +31468,7 @@
         <v>45520</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -31546,7 +31546,7 @@
         <v>46215</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -31619,7 +31619,7 @@
         <v>46216</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -31692,7 +31692,7 @@
         <v>46216</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -31765,7 +31765,7 @@
         <v>45113</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -31843,7 +31843,7 @@
         <v>46215</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -31916,7 +31916,7 @@
         <v>46175</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -31989,7 +31989,7 @@
         <v>45763</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -32067,7 +32067,7 @@
         <v>45224</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -32145,7 +32145,7 @@
         <v>46266</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -32223,7 +32223,7 @@
         <v>45474</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -32301,7 +32301,7 @@
         <v>45505</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -32379,7 +32379,7 @@
         <v>45565</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -32457,7 +32457,7 @@
         <v>45124</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -32535,7 +32535,7 @@
         <v>46009</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -32608,7 +32608,7 @@
         <v>46274</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -32686,7 +32686,7 @@
         <v>46281</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -32764,7 +32764,7 @@
         <v>45113</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -32842,7 +32842,7 @@
         <v>44841</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -32920,7 +32920,7 @@
         <v>46238</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -32998,7 +32998,7 @@
         <v>46281</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -33076,7 +33076,7 @@
         <v>45555</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -33149,7 +33149,7 @@
         <v>46281</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -33227,7 +33227,7 @@
         <v>46281</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -33305,7 +33305,7 @@
         <v>46237</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -33378,7 +33378,7 @@
         <v>46281</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -33456,7 +33456,7 @@
         <v>44866</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -33534,7 +33534,7 @@
         <v>45590</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -33612,7 +33612,7 @@
         <v>46077</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -33685,7 +33685,7 @@
         <v>45078</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -33763,7 +33763,7 @@
         <v>46288</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -33841,7 +33841,7 @@
         <v>46289</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -33919,7 +33919,7 @@
         <v>46248</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -33992,7 +33992,7 @@
         <v>46170</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -34065,7 +34065,7 @@
         <v>45028</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -34138,7 +34138,7 @@
         <v>45093</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -34216,7 +34216,7 @@
         <v>44854</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -34294,7 +34294,7 @@
         <v>46247</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -34367,7 +34367,7 @@
         <v>45471</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -34445,7 +34445,7 @@
         <v>44984</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -34523,7 +34523,7 @@
         <v>46174</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -34601,7 +34601,7 @@
         <v>46248</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -34674,7 +34674,7 @@
         <v>44841</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -34752,7 +34752,7 @@
         <v>44841</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -34830,7 +34830,7 @@
         <v>44984</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -34908,7 +34908,7 @@
         <v>44984</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -34986,7 +34986,7 @@
         <v>44984</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -35064,7 +35064,7 @@
         <v>44984</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -35137,7 +35137,7 @@
         <v>44984</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -35215,7 +35215,7 @@
         <v>46253</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -35288,7 +35288,7 @@
         <v>45490</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -35361,7 +35361,7 @@
         <v>45022</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -35439,7 +35439,7 @@
         <v>46294</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -35517,7 +35517,7 @@
         <v>45576</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -35595,7 +35595,7 @@
         <v>46295</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -35673,7 +35673,7 @@
         <v>46254</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -35751,7 +35751,7 @@
         <v>46255</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -35824,7 +35824,7 @@
         <v>45555</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -35902,7 +35902,7 @@
         <v>45490</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -35975,7 +35975,7 @@
         <v>45490</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -36048,7 +36048,7 @@
         <v>45490</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -36121,7 +36121,7 @@
         <v>45490</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -36194,7 +36194,7 @@
         <v>45057</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -36272,7 +36272,7 @@
         <v>45073</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -36350,7 +36350,7 @@
         <v>45565</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -36423,7 +36423,7 @@
         <v>44477</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -36496,7 +36496,7 @@
         <v>44823</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -36574,7 +36574,7 @@
         <v>44820</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -36647,7 +36647,7 @@
         <v>45392</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -36720,7 +36720,7 @@
         <v>44823</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -36798,7 +36798,7 @@
         <v>45327</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -36871,7 +36871,7 @@
         <v>45327</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -36944,7 +36944,7 @@
         <v>44824</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -37022,7 +37022,7 @@
         <v>45756</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -37095,7 +37095,7 @@
         <v>45841</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -37173,7 +37173,7 @@
         <v>46147</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -37246,7 +37246,7 @@
         <v>46147</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -37319,7 +37319,7 @@
         <v>46147</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -37392,7 +37392,7 @@
         <v>46148</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -37465,7 +37465,7 @@
         <v>46148</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>

--- a/Översikt JOKKMOKK.xlsx
+++ b/Översikt JOKKMOKK.xlsx
@@ -601,7 +601,7 @@
         <v>45680</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -766,7 +766,7 @@
         <v>45971</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -918,7 +918,7 @@
         <v>46230</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1067,7 +1067,7 @@
         <v>46043</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1205,7 +1205,7 @@
         <v>46184</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1346,7 +1346,7 @@
         <v>46177</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1486,7 +1486,7 @@
         <v>44917</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1624,7 +1624,7 @@
         <v>44539</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1760,7 +1760,7 @@
         <v>46244</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1896,7 +1896,7 @@
         <v>44824</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>45222</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2165,7 +2165,7 @@
         <v>45672</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2297,7 +2297,7 @@
         <v>44781</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2424,7 +2424,7 @@
         <v>45805</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2556,7 +2556,7 @@
         <v>46010</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2683,7 +2683,7 @@
         <v>45476</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2810,7 +2810,7 @@
         <v>45985</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2937,7 +2937,7 @@
         <v>45237</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -3068,7 +3068,7 @@
         <v>45649</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3197,7 +3197,7 @@
         <v>45993</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3321,7 +3321,7 @@
         <v>44474</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3452,7 +3452,7 @@
         <v>45484</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3579,7 +3579,7 @@
         <v>44722</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3702,7 +3702,7 @@
         <v>45174</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3829,7 +3829,7 @@
         <v>45672</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3956,7 +3956,7 @@
         <v>45649</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -4080,7 +4080,7 @@
         <v>44552</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -4199,7 +4199,7 @@
         <v>45986</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4318,7 +4318,7 @@
         <v>45994</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4437,7 +4437,7 @@
         <v>45596</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4560,7 +4560,7 @@
         <v>46184</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4683,7 +4683,7 @@
         <v>45476</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4801,7 +4801,7 @@
         <v>45810</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4918,7 +4918,7 @@
         <v>45113</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -5036,7 +5036,7 @@
         <v>46283</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -5158,7 +5158,7 @@
         <v>46042</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -5279,7 +5279,7 @@
         <v>45940</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5395,7 +5395,7 @@
         <v>46184</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5511,7 +5511,7 @@
         <v>46101</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5626,7 +5626,7 @@
         <v>46149</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5736,7 +5736,7 @@
         <v>44722</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5851,7 +5851,7 @@
         <v>45484</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5965,7 +5965,7 @@
         <v>44490</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -6079,7 +6079,7 @@
         <v>45609</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -6197,7 +6197,7 @@
         <v>46184</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -6311,7 +6311,7 @@
         <v>46090</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6420,7 +6420,7 @@
         <v>45114</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6533,7 +6533,7 @@
         <v>45170</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6646,7 +6646,7 @@
         <v>46113</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6759,7 +6759,7 @@
         <v>46206</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6867,7 +6867,7 @@
         <v>46213</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6979,7 +6979,7 @@
         <v>45748</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -7086,7 +7086,7 @@
         <v>45134</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -7193,7 +7193,7 @@
         <v>46013</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -7305,7 +7305,7 @@
         <v>45649</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -7421,7 +7421,7 @@
         <v>44545</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7528,7 +7528,7 @@
         <v>45012</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7635,7 +7635,7 @@
         <v>44825</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7751,7 +7751,7 @@
         <v>44810</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7861,7 +7861,7 @@
         <v>44726</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7972,7 +7972,7 @@
         <v>44824</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -8083,7 +8083,7 @@
         <v>45891</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -8194,7 +8194,7 @@
         <v>45891</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -8309,7 +8309,7 @@
         <v>45897</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -8420,7 +8420,7 @@
         <v>45951</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8531,7 +8531,7 @@
         <v>45992</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8642,7 +8642,7 @@
         <v>46178</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8753,7 +8753,7 @@
         <v>45113</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8864,7 +8864,7 @@
         <v>46184</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8975,7 +8975,7 @@
         <v>46184</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -9086,7 +9086,7 @@
         <v>46213</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -9197,7 +9197,7 @@
         <v>46184</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -9308,7 +9308,7 @@
         <v>46261</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -9418,7 +9418,7 @@
         <v>45035</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -9529,7 +9529,7 @@
         <v>46027</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9634,7 +9634,7 @@
         <v>45799</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9748,7 +9748,7 @@
         <v>45919</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9858,7 +9858,7 @@
         <v>45572</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9968,7 +9968,7 @@
         <v>45944</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -10078,7 +10078,7 @@
         <v>45951</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -10188,7 +10188,7 @@
         <v>45958</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -10298,7 +10298,7 @@
         <v>44545</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -10403,7 +10403,7 @@
         <v>45974</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -10513,7 +10513,7 @@
         <v>45974</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -10623,7 +10623,7 @@
         <v>45819</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10733,7 +10733,7 @@
         <v>45982</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10847,7 +10847,7 @@
         <v>45985</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10957,7 +10957,7 @@
         <v>45826</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -11067,7 +11067,7 @@
         <v>45838</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -11177,7 +11177,7 @@
         <v>46137</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -11287,7 +11287,7 @@
         <v>45225</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -11397,7 +11397,7 @@
         <v>45672</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -11507,7 +11507,7 @@
         <v>45876</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -11617,7 +11617,7 @@
         <v>45608</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11727,7 +11727,7 @@
         <v>45600</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11832,7 +11832,7 @@
         <v>46197</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11942,7 +11942,7 @@
         <v>46199</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -12052,7 +12052,7 @@
         <v>46199</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -12162,7 +12162,7 @@
         <v>45915</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -12272,7 +12272,7 @@
         <v>46276</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -12382,7 +12382,7 @@
         <v>45222</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -12487,7 +12487,7 @@
         <v>46240</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -12597,7 +12597,7 @@
         <v>44865</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -12711,7 +12711,7 @@
         <v>45918</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -12816,7 +12816,7 @@
         <v>46272</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -12926,7 +12926,7 @@
         <v>44967</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -13036,7 +13036,7 @@
         <v>45358</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -13141,7 +13141,7 @@
         <v>44820</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -13219,7 +13219,7 @@
         <v>44676</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -13292,7 +13292,7 @@
         <v>44543</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -13370,7 +13370,7 @@
         <v>44543</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -13448,7 +13448,7 @@
         <v>44543</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -13521,7 +13521,7 @@
         <v>44586</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -13599,7 +13599,7 @@
         <v>44586</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -13677,7 +13677,7 @@
         <v>44663</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -13750,7 +13750,7 @@
         <v>44685</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -13828,7 +13828,7 @@
         <v>44539</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -13906,7 +13906,7 @@
         <v>44543</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -13984,7 +13984,7 @@
         <v>44543</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -14062,7 +14062,7 @@
         <v>44638</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -14140,7 +14140,7 @@
         <v>44743</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -14218,7 +14218,7 @@
         <v>44543</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -14296,7 +14296,7 @@
         <v>44586</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -14374,7 +14374,7 @@
         <v>44573</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -14452,7 +14452,7 @@
         <v>44820</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -14530,7 +14530,7 @@
         <v>44824</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -14608,7 +14608,7 @@
         <v>44532</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -14681,7 +14681,7 @@
         <v>44868</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -14759,7 +14759,7 @@
         <v>45028</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -14832,7 +14832,7 @@
         <v>44966</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -14905,7 +14905,7 @@
         <v>45106</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -14983,7 +14983,7 @@
         <v>44841</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -15061,7 +15061,7 @@
         <v>45884</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -15139,7 +15139,7 @@
         <v>44539</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -15217,7 +15217,7 @@
         <v>45451</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -15295,7 +15295,7 @@
         <v>45596</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -15373,7 +15373,7 @@
         <v>46006</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -15446,7 +15446,7 @@
         <v>45491</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -15519,7 +15519,7 @@
         <v>45586</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -15592,7 +15592,7 @@
         <v>46010</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -15665,7 +15665,7 @@
         <v>45482</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -15738,7 +15738,7 @@
         <v>45463</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -15816,7 +15816,7 @@
         <v>45222</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -15889,7 +15889,7 @@
         <v>45572</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -15967,7 +15967,7 @@
         <v>46021</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -16040,7 +16040,7 @@
         <v>45558</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -16118,7 +16118,7 @@
         <v>46010</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -16191,7 +16191,7 @@
         <v>46010</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -16269,7 +16269,7 @@
         <v>46009</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -16342,7 +16342,7 @@
         <v>45897</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -16420,7 +16420,7 @@
         <v>45993</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -16498,7 +16498,7 @@
         <v>45992</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -16576,7 +16576,7 @@
         <v>45994</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -16654,7 +16654,7 @@
         <v>46030</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -16732,7 +16732,7 @@
         <v>45901</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -16810,7 +16810,7 @@
         <v>45086</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -16883,7 +16883,7 @@
         <v>45482</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -16956,7 +16956,7 @@
         <v>45693</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -17029,7 +17029,7 @@
         <v>45677</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -17107,7 +17107,7 @@
         <v>45904</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -17185,7 +17185,7 @@
         <v>45907</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -17258,7 +17258,7 @@
         <v>45544</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -17336,7 +17336,7 @@
         <v>45912</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -17414,7 +17414,7 @@
         <v>45918</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -17492,7 +17492,7 @@
         <v>45572</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -17570,7 +17570,7 @@
         <v>44984</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -17643,7 +17643,7 @@
         <v>44984</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -17716,7 +17716,7 @@
         <v>45544</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -17794,7 +17794,7 @@
         <v>45259</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -17872,7 +17872,7 @@
         <v>45596</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -17950,7 +17950,7 @@
         <v>45883</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -18028,7 +18028,7 @@
         <v>45349</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -18101,7 +18101,7 @@
         <v>45532</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -18174,7 +18174,7 @@
         <v>45124</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -18252,7 +18252,7 @@
         <v>45572</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -18330,7 +18330,7 @@
         <v>45887</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -18408,7 +18408,7 @@
         <v>45928</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -18486,7 +18486,7 @@
         <v>44984</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -18564,7 +18564,7 @@
         <v>44984</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -18642,7 +18642,7 @@
         <v>44984</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -18720,7 +18720,7 @@
         <v>45664</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -18798,7 +18798,7 @@
         <v>45942</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -18876,7 +18876,7 @@
         <v>45942</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -18954,7 +18954,7 @@
         <v>45943</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -19032,7 +19032,7 @@
         <v>45940</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -19110,7 +19110,7 @@
         <v>46077</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -19188,7 +19188,7 @@
         <v>46077</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -19266,7 +19266,7 @@
         <v>46077</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -19344,7 +19344,7 @@
         <v>45679</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -19422,7 +19422,7 @@
         <v>45946</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -19500,7 +19500,7 @@
         <v>46077</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -19578,7 +19578,7 @@
         <v>44873</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -19656,7 +19656,7 @@
         <v>45951</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -19734,7 +19734,7 @@
         <v>45951</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -19812,7 +19812,7 @@
         <v>45951</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -19890,7 +19890,7 @@
         <v>45951</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -19968,7 +19968,7 @@
         <v>45951</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -20046,7 +20046,7 @@
         <v>45951</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -20124,7 +20124,7 @@
         <v>45951</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -20202,7 +20202,7 @@
         <v>45950</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -20275,7 +20275,7 @@
         <v>45950</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -20348,7 +20348,7 @@
         <v>45953</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -20426,7 +20426,7 @@
         <v>44862</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -20499,7 +20499,7 @@
         <v>44984</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -20577,7 +20577,7 @@
         <v>45953</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -20655,7 +20655,7 @@
         <v>45953</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -20733,7 +20733,7 @@
         <v>45953</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -20811,7 +20811,7 @@
         <v>45257</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -20889,7 +20889,7 @@
         <v>45488</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -20962,7 +20962,7 @@
         <v>45323</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -21035,7 +21035,7 @@
         <v>45813</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -21108,7 +21108,7 @@
         <v>45960</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -21181,7 +21181,7 @@
         <v>46092</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -21259,7 +21259,7 @@
         <v>46092</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -21337,7 +21337,7 @@
         <v>46092</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -21415,7 +21415,7 @@
         <v>46092</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -21493,7 +21493,7 @@
         <v>45965</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -21571,7 +21571,7 @@
         <v>45964</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -21649,7 +21649,7 @@
         <v>45124</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -21727,7 +21727,7 @@
         <v>45965</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -21805,7 +21805,7 @@
         <v>45967</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -21878,7 +21878,7 @@
         <v>45646</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -21951,7 +21951,7 @@
         <v>45971</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -22029,7 +22029,7 @@
         <v>45043</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -22107,7 +22107,7 @@
         <v>45968</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -22180,7 +22180,7 @@
         <v>45973</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -22258,7 +22258,7 @@
         <v>45973</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -22336,7 +22336,7 @@
         <v>45516</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -22414,7 +22414,7 @@
         <v>45972</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -22492,7 +22492,7 @@
         <v>45975</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -22570,7 +22570,7 @@
         <v>45974</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -22648,7 +22648,7 @@
         <v>45974</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -22726,7 +22726,7 @@
         <v>45974</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -22804,7 +22804,7 @@
         <v>45974</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -22882,7 +22882,7 @@
         <v>45974</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -22960,7 +22960,7 @@
         <v>45975</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -23033,7 +23033,7 @@
         <v>45974</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -23111,7 +23111,7 @@
         <v>46106</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -23189,7 +23189,7 @@
         <v>46106</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -23267,7 +23267,7 @@
         <v>45979</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -23345,7 +23345,7 @@
         <v>45979</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -23423,7 +23423,7 @@
         <v>45590</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -23501,7 +23501,7 @@
         <v>45517</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -23579,7 +23579,7 @@
         <v>46108</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -23657,7 +23657,7 @@
         <v>45819</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -23735,7 +23735,7 @@
         <v>46108</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -23813,7 +23813,7 @@
         <v>46108</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -23891,7 +23891,7 @@
         <v>46106</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -23969,7 +23969,7 @@
         <v>45985</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -24047,7 +24047,7 @@
         <v>45985</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -24125,7 +24125,7 @@
         <v>46113</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -24203,7 +24203,7 @@
         <v>45721</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -24276,7 +24276,7 @@
         <v>44889</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -24354,7 +24354,7 @@
         <v>46113</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -24432,7 +24432,7 @@
         <v>46113</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -24510,7 +24510,7 @@
         <v>46114</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -24588,7 +24588,7 @@
         <v>46113</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -24666,7 +24666,7 @@
         <v>46113</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -24744,7 +24744,7 @@
         <v>46113</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -24822,7 +24822,7 @@
         <v>45596</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -24900,7 +24900,7 @@
         <v>44841</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -24978,7 +24978,7 @@
         <v>45824</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -25051,7 +25051,7 @@
         <v>45973</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -25129,7 +25129,7 @@
         <v>45993</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -25207,7 +25207,7 @@
         <v>45572</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -25285,7 +25285,7 @@
         <v>44966</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -25363,7 +25363,7 @@
         <v>45995</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -25441,7 +25441,7 @@
         <v>45995</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -25519,7 +25519,7 @@
         <v>45994</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -25597,7 +25597,7 @@
         <v>45827</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -25675,7 +25675,7 @@
         <v>45826</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -25753,7 +25753,7 @@
         <v>46010</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -25826,7 +25826,7 @@
         <v>45953</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -25904,7 +25904,7 @@
         <v>45474</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -25982,7 +25982,7 @@
         <v>45474</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -26060,7 +26060,7 @@
         <v>45474</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -26138,7 +26138,7 @@
         <v>45838</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -26216,7 +26216,7 @@
         <v>45491</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -26289,7 +26289,7 @@
         <v>44493</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -26367,7 +26367,7 @@
         <v>45216</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -26445,7 +26445,7 @@
         <v>45028</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -26518,7 +26518,7 @@
         <v>46137</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -26596,7 +26596,7 @@
         <v>45904</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -26669,7 +26669,7 @@
         <v>44984</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -26747,7 +26747,7 @@
         <v>44589</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -26820,7 +26820,7 @@
         <v>45868</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -26893,7 +26893,7 @@
         <v>45807</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -26971,7 +26971,7 @@
         <v>45168</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -27049,7 +27049,7 @@
         <v>45111</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -27122,7 +27122,7 @@
         <v>45166</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -27195,7 +27195,7 @@
         <v>45608</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -27268,7 +27268,7 @@
         <v>44477</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -27341,7 +27341,7 @@
         <v>46083</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -27414,7 +27414,7 @@
         <v>45903</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -27492,7 +27492,7 @@
         <v>45842</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -27570,7 +27570,7 @@
         <v>45073</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -27648,7 +27648,7 @@
         <v>45824</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -27721,7 +27721,7 @@
         <v>46162</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -27799,7 +27799,7 @@
         <v>45113</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -27877,7 +27877,7 @@
         <v>46164</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -27955,7 +27955,7 @@
         <v>45860</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -28028,7 +28028,7 @@
         <v>45883</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -28106,7 +28106,7 @@
         <v>45880</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -28184,7 +28184,7 @@
         <v>46170</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -28262,7 +28262,7 @@
         <v>46170</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -28335,7 +28335,7 @@
         <v>45474</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -28413,7 +28413,7 @@
         <v>45474</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -28491,7 +28491,7 @@
         <v>45397</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -28569,7 +28569,7 @@
         <v>45883</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -28647,7 +28647,7 @@
         <v>44868</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -28720,7 +28720,7 @@
         <v>46177</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -28798,7 +28798,7 @@
         <v>46177</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -28876,7 +28876,7 @@
         <v>46178</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -28954,7 +28954,7 @@
         <v>46177</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -29032,7 +29032,7 @@
         <v>46177</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -29110,7 +29110,7 @@
         <v>46183</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -29188,7 +29188,7 @@
         <v>44477</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -29261,7 +29261,7 @@
         <v>46185</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -29339,7 +29339,7 @@
         <v>45604</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -29417,7 +29417,7 @@
         <v>46191</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -29495,7 +29495,7 @@
         <v>46191</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -29573,7 +29573,7 @@
         <v>46192</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -29651,7 +29651,7 @@
         <v>45678</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -29729,7 +29729,7 @@
         <v>45090</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -29802,7 +29802,7 @@
         <v>46198</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -29875,7 +29875,7 @@
         <v>45986</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -29948,7 +29948,7 @@
         <v>45474</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -30026,7 +30026,7 @@
         <v>45613</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -30099,7 +30099,7 @@
         <v>45526</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -30172,7 +30172,7 @@
         <v>46197</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -30250,7 +30250,7 @@
         <v>46197</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -30328,7 +30328,7 @@
         <v>46197</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -30406,7 +30406,7 @@
         <v>46199</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -30484,7 +30484,7 @@
         <v>46199</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -30562,7 +30562,7 @@
         <v>44802</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -30635,7 +30635,7 @@
         <v>46199</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -30713,7 +30713,7 @@
         <v>44851</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -30786,7 +30786,7 @@
         <v>45534</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -30864,7 +30864,7 @@
         <v>46204</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -30942,7 +30942,7 @@
         <v>46205</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -31015,7 +31015,7 @@
         <v>46206</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -31088,7 +31088,7 @@
         <v>46206</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -31161,7 +31161,7 @@
         <v>46205</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -31234,7 +31234,7 @@
         <v>46212</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -31312,7 +31312,7 @@
         <v>46211</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -31390,7 +31390,7 @@
         <v>46212</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -31468,7 +31468,7 @@
         <v>45520</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -31546,7 +31546,7 @@
         <v>46215</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -31619,7 +31619,7 @@
         <v>46216</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -31692,7 +31692,7 @@
         <v>46216</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -31765,7 +31765,7 @@
         <v>45113</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -31843,7 +31843,7 @@
         <v>46215</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -31916,7 +31916,7 @@
         <v>46175</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -31989,7 +31989,7 @@
         <v>45763</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -32067,7 +32067,7 @@
         <v>45224</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -32145,7 +32145,7 @@
         <v>46266</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -32223,7 +32223,7 @@
         <v>45474</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -32301,7 +32301,7 @@
         <v>45505</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -32379,7 +32379,7 @@
         <v>45565</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -32457,7 +32457,7 @@
         <v>45124</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -32535,7 +32535,7 @@
         <v>46009</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -32608,7 +32608,7 @@
         <v>46274</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -32686,7 +32686,7 @@
         <v>46281</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -32764,7 +32764,7 @@
         <v>45113</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -32842,7 +32842,7 @@
         <v>44841</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -32920,7 +32920,7 @@
         <v>46238</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -32998,7 +32998,7 @@
         <v>46281</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -33076,7 +33076,7 @@
         <v>45555</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -33149,7 +33149,7 @@
         <v>46281</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -33227,7 +33227,7 @@
         <v>46281</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -33305,7 +33305,7 @@
         <v>46237</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -33378,7 +33378,7 @@
         <v>46281</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -33456,7 +33456,7 @@
         <v>44866</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -33534,7 +33534,7 @@
         <v>45590</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -33612,7 +33612,7 @@
         <v>46077</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -33685,7 +33685,7 @@
         <v>45078</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -33763,7 +33763,7 @@
         <v>46288</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -33841,7 +33841,7 @@
         <v>46289</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -33919,7 +33919,7 @@
         <v>46248</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -33992,7 +33992,7 @@
         <v>46170</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -34065,7 +34065,7 @@
         <v>45028</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -34138,7 +34138,7 @@
         <v>45093</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -34216,7 +34216,7 @@
         <v>44854</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -34294,7 +34294,7 @@
         <v>46247</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -34367,7 +34367,7 @@
         <v>45471</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -34445,7 +34445,7 @@
         <v>44984</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -34523,7 +34523,7 @@
         <v>46174</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -34601,7 +34601,7 @@
         <v>46248</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -34674,7 +34674,7 @@
         <v>44841</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -34752,7 +34752,7 @@
         <v>44841</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -34830,7 +34830,7 @@
         <v>44984</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -34908,7 +34908,7 @@
         <v>44984</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -34986,7 +34986,7 @@
         <v>44984</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -35064,7 +35064,7 @@
         <v>44984</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -35137,7 +35137,7 @@
         <v>44984</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -35215,7 +35215,7 @@
         <v>46253</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -35288,7 +35288,7 @@
         <v>45490</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -35361,7 +35361,7 @@
         <v>45022</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -35439,7 +35439,7 @@
         <v>46294</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -35517,7 +35517,7 @@
         <v>45576</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -35595,7 +35595,7 @@
         <v>46295</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -35673,7 +35673,7 @@
         <v>46254</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -35751,7 +35751,7 @@
         <v>46255</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -35824,7 +35824,7 @@
         <v>45555</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -35902,7 +35902,7 @@
         <v>45490</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -35975,7 +35975,7 @@
         <v>45490</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -36048,7 +36048,7 @@
         <v>45490</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -36121,7 +36121,7 @@
         <v>45490</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -36194,7 +36194,7 @@
         <v>45057</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -36272,7 +36272,7 @@
         <v>45073</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -36350,7 +36350,7 @@
         <v>45565</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -36423,7 +36423,7 @@
         <v>44477</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -36496,7 +36496,7 @@
         <v>44823</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -36574,7 +36574,7 @@
         <v>44820</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -36647,7 +36647,7 @@
         <v>45392</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -36720,7 +36720,7 @@
         <v>44823</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -36798,7 +36798,7 @@
         <v>45327</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -36871,7 +36871,7 @@
         <v>45327</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -36944,7 +36944,7 @@
         <v>44824</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -37022,7 +37022,7 @@
         <v>45756</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -37095,7 +37095,7 @@
         <v>45841</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -37173,7 +37173,7 @@
         <v>46147</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -37246,7 +37246,7 @@
         <v>46147</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -37319,7 +37319,7 @@
         <v>46147</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -37392,7 +37392,7 @@
         <v>46148</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -37465,7 +37465,7 @@
         <v>46148</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>

--- a/Översikt JOKKMOKK.xlsx
+++ b/Översikt JOKKMOKK.xlsx
@@ -601,7 +601,7 @@
         <v>45680</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -766,7 +766,7 @@
         <v>45971</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -918,7 +918,7 @@
         <v>46230</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1067,7 +1067,7 @@
         <v>46043</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1205,7 +1205,7 @@
         <v>46184</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1346,7 +1346,7 @@
         <v>46177</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1486,7 +1486,7 @@
         <v>44917</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1624,7 +1624,7 @@
         <v>44539</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1760,7 +1760,7 @@
         <v>46244</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1896,7 +1896,7 @@
         <v>44824</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>45222</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2165,7 +2165,7 @@
         <v>46010</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2293,7 +2293,7 @@
         <v>45476</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2420,7 +2420,7 @@
         <v>45672</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2552,7 +2552,7 @@
         <v>44781</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2679,7 +2679,7 @@
         <v>45805</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2811,7 +2811,7 @@
         <v>45985</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2938,7 +2938,7 @@
         <v>45237</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -3069,7 +3069,7 @@
         <v>45649</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3198,7 +3198,7 @@
         <v>45993</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3322,7 +3322,7 @@
         <v>45672</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3449,7 +3449,7 @@
         <v>44722</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3572,7 +3572,7 @@
         <v>45174</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3699,7 +3699,7 @@
         <v>45484</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3826,7 +3826,7 @@
         <v>45649</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3950,7 +3950,7 @@
         <v>44552</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -4069,7 +4069,7 @@
         <v>45986</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -4188,7 +4188,7 @@
         <v>45994</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4307,7 +4307,7 @@
         <v>45476</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4425,7 +4425,7 @@
         <v>45596</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4548,7 +4548,7 @@
         <v>46184</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4671,7 +4671,7 @@
         <v>45810</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4788,7 +4788,7 @@
         <v>45113</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4906,7 +4906,7 @@
         <v>46283</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -5028,7 +5028,7 @@
         <v>46042</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -5149,7 +5149,7 @@
         <v>45940</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -5265,7 +5265,7 @@
         <v>46184</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5381,7 +5381,7 @@
         <v>44722</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5496,7 +5496,7 @@
         <v>46101</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5611,7 +5611,7 @@
         <v>46149</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5721,7 +5721,7 @@
         <v>44490</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5835,7 +5835,7 @@
         <v>45609</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5953,7 +5953,7 @@
         <v>45484</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -6067,7 +6067,7 @@
         <v>46184</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -6181,7 +6181,7 @@
         <v>46300</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -6295,7 +6295,7 @@
         <v>46090</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6404,7 +6404,7 @@
         <v>45170</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6517,7 +6517,7 @@
         <v>45114</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6630,7 +6630,7 @@
         <v>46113</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6743,7 +6743,7 @@
         <v>46206</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6851,7 +6851,7 @@
         <v>46213</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6963,7 +6963,7 @@
         <v>45649</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -7079,7 +7079,7 @@
         <v>44545</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -7186,7 +7186,7 @@
         <v>45748</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -7293,7 +7293,7 @@
         <v>45134</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -7400,7 +7400,7 @@
         <v>46013</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7512,7 +7512,7 @@
         <v>45012</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7619,7 +7619,7 @@
         <v>44825</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7735,7 +7735,7 @@
         <v>44810</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7845,7 +7845,7 @@
         <v>44726</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7956,7 +7956,7 @@
         <v>44824</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -8067,7 +8067,7 @@
         <v>45891</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -8178,7 +8178,7 @@
         <v>45891</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -8293,7 +8293,7 @@
         <v>45897</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -8404,7 +8404,7 @@
         <v>45951</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8515,7 +8515,7 @@
         <v>45992</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8626,7 +8626,7 @@
         <v>46178</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8737,7 +8737,7 @@
         <v>46184</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8848,7 +8848,7 @@
         <v>46184</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8959,7 +8959,7 @@
         <v>46213</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -9070,7 +9070,7 @@
         <v>46184</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -9181,7 +9181,7 @@
         <v>46300</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -9291,7 +9291,7 @@
         <v>46302</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -9406,7 +9406,7 @@
         <v>46261</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -9516,7 +9516,7 @@
         <v>45113</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9627,7 +9627,7 @@
         <v>45035</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9738,7 +9738,7 @@
         <v>45225</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9848,7 +9848,7 @@
         <v>45222</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9953,7 +9953,7 @@
         <v>45919</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -10063,7 +10063,7 @@
         <v>45799</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -10177,7 +10177,7 @@
         <v>45944</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -10287,7 +10287,7 @@
         <v>45819</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -10397,7 +10397,7 @@
         <v>45826</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -10507,7 +10507,7 @@
         <v>45951</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -10617,7 +10617,7 @@
         <v>45958</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10727,7 +10727,7 @@
         <v>44545</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10832,7 +10832,7 @@
         <v>45838</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10942,7 +10942,7 @@
         <v>45974</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -11052,7 +11052,7 @@
         <v>45974</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -11162,7 +11162,7 @@
         <v>45876</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -11272,7 +11272,7 @@
         <v>45982</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -11386,7 +11386,7 @@
         <v>45672</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -11496,7 +11496,7 @@
         <v>45985</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -11606,7 +11606,7 @@
         <v>44865</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11720,7 +11720,7 @@
         <v>46027</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11825,7 +11825,7 @@
         <v>46137</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11935,7 +11935,7 @@
         <v>45572</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -12045,7 +12045,7 @@
         <v>45608</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -12155,7 +12155,7 @@
         <v>45600</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -12260,7 +12260,7 @@
         <v>46197</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -12370,7 +12370,7 @@
         <v>46199</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -12480,7 +12480,7 @@
         <v>46199</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -12590,7 +12590,7 @@
         <v>45915</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -12700,7 +12700,7 @@
         <v>46276</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -12810,7 +12810,7 @@
         <v>46240</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -12920,7 +12920,7 @@
         <v>45918</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -13025,7 +13025,7 @@
         <v>46272</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -13135,7 +13135,7 @@
         <v>44967</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -13245,7 +13245,7 @@
         <v>45358</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -13350,7 +13350,7 @@
         <v>44820</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -13428,7 +13428,7 @@
         <v>44676</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -13501,7 +13501,7 @@
         <v>44543</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -13579,7 +13579,7 @@
         <v>44543</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -13657,7 +13657,7 @@
         <v>44543</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -13730,7 +13730,7 @@
         <v>44586</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -13808,7 +13808,7 @@
         <v>44586</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -13886,7 +13886,7 @@
         <v>44663</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -13959,7 +13959,7 @@
         <v>44685</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -14037,7 +14037,7 @@
         <v>44543</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -14115,7 +14115,7 @@
         <v>44824</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -14193,7 +14193,7 @@
         <v>44539</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -14271,7 +14271,7 @@
         <v>44743</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -14349,7 +14349,7 @@
         <v>44543</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -14427,7 +14427,7 @@
         <v>44586</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -14505,7 +14505,7 @@
         <v>44543</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -14583,7 +14583,7 @@
         <v>44573</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -14661,7 +14661,7 @@
         <v>44638</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -14739,7 +14739,7 @@
         <v>44820</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -14817,7 +14817,7 @@
         <v>44862</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -14890,7 +14890,7 @@
         <v>44532</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -14963,7 +14963,7 @@
         <v>44868</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -15041,7 +15041,7 @@
         <v>44841</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -15119,7 +15119,7 @@
         <v>45022</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -15197,7 +15197,7 @@
         <v>45090</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -15270,7 +15270,7 @@
         <v>45086</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -15343,7 +15343,7 @@
         <v>45482</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -15416,7 +15416,7 @@
         <v>45679</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -15494,7 +15494,7 @@
         <v>45534</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -15572,7 +15572,7 @@
         <v>44873</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -15650,7 +15650,7 @@
         <v>45474</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -15728,7 +15728,7 @@
         <v>45113</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -15806,7 +15806,7 @@
         <v>45106</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -15884,7 +15884,7 @@
         <v>44868</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -15957,7 +15957,7 @@
         <v>44866</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -16035,7 +16035,7 @@
         <v>44841</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -16113,7 +16113,7 @@
         <v>45397</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -16191,7 +16191,7 @@
         <v>45474</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -16269,7 +16269,7 @@
         <v>45474</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -16347,7 +16347,7 @@
         <v>45474</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -16425,7 +16425,7 @@
         <v>45474</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -16503,7 +16503,7 @@
         <v>45474</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -16581,7 +16581,7 @@
         <v>44589</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -16654,7 +16654,7 @@
         <v>45471</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -16732,7 +16732,7 @@
         <v>45463</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -16810,7 +16810,7 @@
         <v>45482</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -16883,7 +16883,7 @@
         <v>45884</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -16961,7 +16961,7 @@
         <v>45555</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -17039,7 +17039,7 @@
         <v>45883</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -17117,7 +17117,7 @@
         <v>45078</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -17195,7 +17195,7 @@
         <v>44966</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -17268,7 +17268,7 @@
         <v>44493</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -17346,7 +17346,7 @@
         <v>45505</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -17424,7 +17424,7 @@
         <v>45897</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -17502,7 +17502,7 @@
         <v>45490</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -17575,7 +17575,7 @@
         <v>45222</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -17648,7 +17648,7 @@
         <v>45901</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -17726,7 +17726,7 @@
         <v>44841</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -17804,7 +17804,7 @@
         <v>45124</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -17882,7 +17882,7 @@
         <v>45216</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -17960,7 +17960,7 @@
         <v>45093</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -18038,7 +18038,7 @@
         <v>45904</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -18116,7 +18116,7 @@
         <v>44984</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -18194,7 +18194,7 @@
         <v>45490</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -18267,7 +18267,7 @@
         <v>45490</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -18340,7 +18340,7 @@
         <v>45490</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -18413,7 +18413,7 @@
         <v>45490</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -18486,7 +18486,7 @@
         <v>45907</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -18559,7 +18559,7 @@
         <v>45073</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -18637,7 +18637,7 @@
         <v>45912</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -18715,7 +18715,7 @@
         <v>45491</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -18788,7 +18788,7 @@
         <v>45646</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -18861,7 +18861,7 @@
         <v>44539</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -18939,7 +18939,7 @@
         <v>45558</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -19017,7 +19017,7 @@
         <v>45166</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -19090,7 +19090,7 @@
         <v>45918</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -19168,7 +19168,7 @@
         <v>45664</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -19246,7 +19246,7 @@
         <v>44984</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -19324,7 +19324,7 @@
         <v>44984</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -19402,7 +19402,7 @@
         <v>44984</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -19480,7 +19480,7 @@
         <v>44984</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -19553,7 +19553,7 @@
         <v>44984</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -19631,7 +19631,7 @@
         <v>45491</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -19704,7 +19704,7 @@
         <v>45451</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -19782,7 +19782,7 @@
         <v>45124</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -19860,7 +19860,7 @@
         <v>45572</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -19938,7 +19938,7 @@
         <v>45028</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -20011,7 +20011,7 @@
         <v>45678</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -20089,7 +20089,7 @@
         <v>45928</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -20167,7 +20167,7 @@
         <v>45565</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -20240,7 +20240,7 @@
         <v>45887</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -20318,7 +20318,7 @@
         <v>44984</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -20396,7 +20396,7 @@
         <v>44984</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -20474,7 +20474,7 @@
         <v>45224</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -20552,7 +20552,7 @@
         <v>44984</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -20625,7 +20625,7 @@
         <v>44984</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -20698,7 +20698,7 @@
         <v>45526</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -20771,7 +20771,7 @@
         <v>45586</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -20844,7 +20844,7 @@
         <v>45555</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -20917,7 +20917,7 @@
         <v>45349</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -20990,7 +20990,7 @@
         <v>45259</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -21068,7 +21068,7 @@
         <v>45596</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -21146,7 +21146,7 @@
         <v>45544</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -21224,7 +21224,7 @@
         <v>45532</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -21297,7 +21297,7 @@
         <v>45590</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -21375,7 +21375,7 @@
         <v>45596</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -21453,7 +21453,7 @@
         <v>45940</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -21531,7 +21531,7 @@
         <v>45943</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -21609,7 +21609,7 @@
         <v>45942</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -21687,7 +21687,7 @@
         <v>45942</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -21765,7 +21765,7 @@
         <v>45604</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -21843,7 +21843,7 @@
         <v>45813</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -21916,7 +21916,7 @@
         <v>45946</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -21994,7 +21994,7 @@
         <v>45590</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -22072,7 +22072,7 @@
         <v>45950</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -22145,7 +22145,7 @@
         <v>45950</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -22218,7 +22218,7 @@
         <v>45819</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -22296,7 +22296,7 @@
         <v>45824</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -22369,7 +22369,7 @@
         <v>45826</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -22447,7 +22447,7 @@
         <v>45951</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -22525,7 +22525,7 @@
         <v>45951</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -22603,7 +22603,7 @@
         <v>45565</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -22681,7 +22681,7 @@
         <v>45827</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -22759,7 +22759,7 @@
         <v>45951</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -22837,7 +22837,7 @@
         <v>45951</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -22915,7 +22915,7 @@
         <v>44984</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -22993,7 +22993,7 @@
         <v>45951</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -23071,7 +23071,7 @@
         <v>45951</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -23149,7 +23149,7 @@
         <v>45951</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -23227,7 +23227,7 @@
         <v>45953</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -23305,7 +23305,7 @@
         <v>45953</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -23383,7 +23383,7 @@
         <v>45953</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -23461,7 +23461,7 @@
         <v>45953</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -23539,7 +23539,7 @@
         <v>45960</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -23612,7 +23612,7 @@
         <v>45111</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -23685,7 +23685,7 @@
         <v>45964</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -23763,7 +23763,7 @@
         <v>45965</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -23841,7 +23841,7 @@
         <v>45838</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -23919,7 +23919,7 @@
         <v>45965</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -23997,7 +23997,7 @@
         <v>45968</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -24070,7 +24070,7 @@
         <v>44802</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -24143,7 +24143,7 @@
         <v>45967</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -24216,7 +24216,7 @@
         <v>44851</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -24289,7 +24289,7 @@
         <v>45972</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -24367,7 +24367,7 @@
         <v>45971</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -24445,7 +24445,7 @@
         <v>45974</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -24523,7 +24523,7 @@
         <v>45973</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -24601,7 +24601,7 @@
         <v>45974</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -24679,7 +24679,7 @@
         <v>45973</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -24757,7 +24757,7 @@
         <v>45974</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -24835,7 +24835,7 @@
         <v>45974</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -24913,7 +24913,7 @@
         <v>45974</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -24991,7 +24991,7 @@
         <v>45974</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -25069,7 +25069,7 @@
         <v>45975</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -25142,7 +25142,7 @@
         <v>45124</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -25220,7 +25220,7 @@
         <v>45257</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -25298,7 +25298,7 @@
         <v>45488</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -25371,7 +25371,7 @@
         <v>45807</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -25449,7 +25449,7 @@
         <v>45868</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -25522,7 +25522,7 @@
         <v>45975</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -25600,7 +25600,7 @@
         <v>45028</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -25673,7 +25673,7 @@
         <v>45979</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -25751,7 +25751,7 @@
         <v>45474</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -25829,7 +25829,7 @@
         <v>45979</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -25907,7 +25907,7 @@
         <v>45763</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -25985,7 +25985,7 @@
         <v>45880</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -26063,7 +26063,7 @@
         <v>45985</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -26141,7 +26141,7 @@
         <v>45985</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -26219,7 +26219,7 @@
         <v>45043</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -26297,7 +26297,7 @@
         <v>45973</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -26375,7 +26375,7 @@
         <v>44984</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -26453,7 +26453,7 @@
         <v>46106</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -26531,7 +26531,7 @@
         <v>46106</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -26609,7 +26609,7 @@
         <v>46106</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -26687,7 +26687,7 @@
         <v>46108</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -26765,7 +26765,7 @@
         <v>46108</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -26843,7 +26843,7 @@
         <v>45516</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -26921,7 +26921,7 @@
         <v>45721</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -26994,7 +26994,7 @@
         <v>46108</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -27072,7 +27072,7 @@
         <v>44889</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -27150,7 +27150,7 @@
         <v>46113</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -27228,7 +27228,7 @@
         <v>44984</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -27306,7 +27306,7 @@
         <v>46113</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -27384,7 +27384,7 @@
         <v>46113</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -27462,7 +27462,7 @@
         <v>46113</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -27540,7 +27540,7 @@
         <v>46113</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -27618,7 +27618,7 @@
         <v>46113</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -27696,7 +27696,7 @@
         <v>44841</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -27774,7 +27774,7 @@
         <v>46114</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -27852,7 +27852,7 @@
         <v>45993</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -27930,7 +27930,7 @@
         <v>45994</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -28008,7 +28008,7 @@
         <v>45572</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -28086,7 +28086,7 @@
         <v>45995</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -28164,7 +28164,7 @@
         <v>45995</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -28242,7 +28242,7 @@
         <v>45517</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -28320,7 +28320,7 @@
         <v>45576</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -28398,7 +28398,7 @@
         <v>45953</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -28476,7 +28476,7 @@
         <v>44966</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -28554,7 +28554,7 @@
         <v>46010</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -28627,7 +28627,7 @@
         <v>45113</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -28705,7 +28705,7 @@
         <v>46006</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -28778,7 +28778,7 @@
         <v>45073</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -28856,7 +28856,7 @@
         <v>45323</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -28929,7 +28929,7 @@
         <v>46010</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -29002,7 +29002,7 @@
         <v>45028</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -29075,7 +29075,7 @@
         <v>45572</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -29153,7 +29153,7 @@
         <v>45596</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -29231,7 +29231,7 @@
         <v>46021</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -29304,7 +29304,7 @@
         <v>46010</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -29377,7 +29377,7 @@
         <v>46010</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -29455,7 +29455,7 @@
         <v>46009</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -29528,7 +29528,7 @@
         <v>46030</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -29606,7 +29606,7 @@
         <v>45994</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -29684,7 +29684,7 @@
         <v>45057</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -29762,7 +29762,7 @@
         <v>46137</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -29840,7 +29840,7 @@
         <v>45113</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -29918,7 +29918,7 @@
         <v>45992</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -29996,7 +29996,7 @@
         <v>45993</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -30074,7 +30074,7 @@
         <v>45693</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -30147,7 +30147,7 @@
         <v>45544</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -30225,7 +30225,7 @@
         <v>45677</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -30303,7 +30303,7 @@
         <v>45168</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -30381,7 +30381,7 @@
         <v>45904</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -30454,7 +30454,7 @@
         <v>45883</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -30532,7 +30532,7 @@
         <v>45572</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -30610,7 +30610,7 @@
         <v>45608</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -30683,7 +30683,7 @@
         <v>46077</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -30761,7 +30761,7 @@
         <v>46077</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -30839,7 +30839,7 @@
         <v>46077</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -30917,7 +30917,7 @@
         <v>46077</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -30995,7 +30995,7 @@
         <v>45903</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -31073,7 +31073,7 @@
         <v>46083</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -31146,7 +31146,7 @@
         <v>46092</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -31224,7 +31224,7 @@
         <v>46092</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -31302,7 +31302,7 @@
         <v>45842</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -31380,7 +31380,7 @@
         <v>46092</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -31458,7 +31458,7 @@
         <v>46092</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -31536,7 +31536,7 @@
         <v>46162</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -31614,7 +31614,7 @@
         <v>46164</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -31692,7 +31692,7 @@
         <v>45860</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -31765,7 +31765,7 @@
         <v>45824</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -31838,7 +31838,7 @@
         <v>45883</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -31916,7 +31916,7 @@
         <v>46170</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -31994,7 +31994,7 @@
         <v>46170</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -32067,7 +32067,7 @@
         <v>46177</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -32145,7 +32145,7 @@
         <v>46177</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -32223,7 +32223,7 @@
         <v>46177</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -32301,7 +32301,7 @@
         <v>46177</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -32379,7 +32379,7 @@
         <v>46178</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -32457,7 +32457,7 @@
         <v>46183</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -32535,7 +32535,7 @@
         <v>46185</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -32613,7 +32613,7 @@
         <v>46191</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -32691,7 +32691,7 @@
         <v>46192</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -32769,7 +32769,7 @@
         <v>46191</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -32847,7 +32847,7 @@
         <v>45613</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -32920,7 +32920,7 @@
         <v>46197</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -32998,7 +32998,7 @@
         <v>46197</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -33076,7 +33076,7 @@
         <v>46197</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -33154,7 +33154,7 @@
         <v>45986</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -33227,7 +33227,7 @@
         <v>46199</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -33305,7 +33305,7 @@
         <v>46199</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -33383,7 +33383,7 @@
         <v>46199</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -33461,7 +33461,7 @@
         <v>46198</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -33534,7 +33534,7 @@
         <v>46205</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -33607,7 +33607,7 @@
         <v>46204</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -33685,7 +33685,7 @@
         <v>46205</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -33758,7 +33758,7 @@
         <v>46206</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -33831,7 +33831,7 @@
         <v>46206</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -33904,7 +33904,7 @@
         <v>46211</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -33982,7 +33982,7 @@
         <v>46215</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -34055,7 +34055,7 @@
         <v>46215</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -34128,7 +34128,7 @@
         <v>46212</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -34206,7 +34206,7 @@
         <v>46212</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -34284,7 +34284,7 @@
         <v>45520</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -34362,7 +34362,7 @@
         <v>46216</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -34435,7 +34435,7 @@
         <v>46175</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -34508,7 +34508,7 @@
         <v>46216</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -34581,7 +34581,7 @@
         <v>46266</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -34659,7 +34659,7 @@
         <v>46274</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -34737,7 +34737,7 @@
         <v>46009</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -34810,7 +34810,7 @@
         <v>46237</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -34883,7 +34883,7 @@
         <v>44841</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -34961,7 +34961,7 @@
         <v>46281</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -35039,7 +35039,7 @@
         <v>46281</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -35117,7 +35117,7 @@
         <v>46281</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -35195,7 +35195,7 @@
         <v>46281</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -35273,7 +35273,7 @@
         <v>46238</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -35351,7 +35351,7 @@
         <v>46281</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -35429,7 +35429,7 @@
         <v>46288</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -35507,7 +35507,7 @@
         <v>46077</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -35580,7 +35580,7 @@
         <v>44854</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -35658,7 +35658,7 @@
         <v>46289</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -35736,7 +35736,7 @@
         <v>46170</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -35809,7 +35809,7 @@
         <v>46174</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -35887,7 +35887,7 @@
         <v>46247</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -35960,7 +35960,7 @@
         <v>46248</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -36033,7 +36033,7 @@
         <v>46248</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -36106,7 +36106,7 @@
         <v>46294</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -36184,7 +36184,7 @@
         <v>46253</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -36257,7 +36257,7 @@
         <v>46255</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -36330,7 +36330,7 @@
         <v>46300</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -36408,7 +36408,7 @@
         <v>46300</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -36486,7 +36486,7 @@
         <v>46300</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -36564,7 +36564,7 @@
         <v>46300</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -36642,7 +36642,7 @@
         <v>46295</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -36720,7 +36720,7 @@
         <v>46300</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -36798,7 +36798,7 @@
         <v>46254</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -36876,7 +36876,7 @@
         <v>46301</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -36954,7 +36954,7 @@
         <v>46301</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -37032,7 +37032,7 @@
         <v>46303</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -37110,7 +37110,7 @@
         <v>46304</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -37188,7 +37188,7 @@
         <v>44823</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -37266,7 +37266,7 @@
         <v>44820</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -37339,7 +37339,7 @@
         <v>45392</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -37412,7 +37412,7 @@
         <v>44823</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -37490,7 +37490,7 @@
         <v>45327</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -37563,7 +37563,7 @@
         <v>45327</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -37636,7 +37636,7 @@
         <v>44824</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -37714,7 +37714,7 @@
         <v>45756</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -37787,7 +37787,7 @@
         <v>45841</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -37865,7 +37865,7 @@
         <v>46147</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -37938,7 +37938,7 @@
         <v>46147</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -38011,7 +38011,7 @@
         <v>46147</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -38084,7 +38084,7 @@
         <v>46148</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -38157,7 +38157,7 @@
         <v>46148</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>

--- a/Översikt JOKKMOKK.xlsx
+++ b/Översikt JOKKMOKK.xlsx
@@ -601,7 +601,7 @@
         <v>45680</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -766,7 +766,7 @@
         <v>45971</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -918,7 +918,7 @@
         <v>46230</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1067,7 +1067,7 @@
         <v>46043</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1205,7 +1205,7 @@
         <v>46184</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1346,7 +1346,7 @@
         <v>46177</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1486,7 +1486,7 @@
         <v>44917</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1624,7 +1624,7 @@
         <v>44539</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1760,7 +1760,7 @@
         <v>46244</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1896,7 +1896,7 @@
         <v>44824</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>45222</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2165,7 +2165,7 @@
         <v>46010</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2293,7 +2293,7 @@
         <v>45476</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2420,7 +2420,7 @@
         <v>45672</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2552,7 +2552,7 @@
         <v>44781</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2679,7 +2679,7 @@
         <v>45805</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2811,7 +2811,7 @@
         <v>45985</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2938,7 +2938,7 @@
         <v>45237</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -3069,7 +3069,7 @@
         <v>45649</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3198,7 +3198,7 @@
         <v>45993</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3322,7 +3322,7 @@
         <v>45672</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3449,7 +3449,7 @@
         <v>44722</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3572,7 +3572,7 @@
         <v>45174</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3699,7 +3699,7 @@
         <v>45484</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3826,7 +3826,7 @@
         <v>45649</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3950,7 +3950,7 @@
         <v>44552</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -4069,7 +4069,7 @@
         <v>45986</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -4188,7 +4188,7 @@
         <v>45994</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4307,7 +4307,7 @@
         <v>45476</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4425,7 +4425,7 @@
         <v>45596</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4548,7 +4548,7 @@
         <v>46184</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4671,7 +4671,7 @@
         <v>45810</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4788,7 +4788,7 @@
         <v>45113</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4906,7 +4906,7 @@
         <v>46283</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -5028,7 +5028,7 @@
         <v>46042</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -5149,7 +5149,7 @@
         <v>45940</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -5265,7 +5265,7 @@
         <v>46184</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5381,7 +5381,7 @@
         <v>44722</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5496,7 +5496,7 @@
         <v>46101</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5611,7 +5611,7 @@
         <v>46149</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5721,7 +5721,7 @@
         <v>44490</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5835,7 +5835,7 @@
         <v>45609</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5953,7 +5953,7 @@
         <v>45484</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -6067,7 +6067,7 @@
         <v>46184</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -6181,7 +6181,7 @@
         <v>46300</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -6295,7 +6295,7 @@
         <v>46090</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6404,7 +6404,7 @@
         <v>45170</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6517,7 +6517,7 @@
         <v>45114</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6630,7 +6630,7 @@
         <v>46113</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6743,7 +6743,7 @@
         <v>46206</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6851,7 +6851,7 @@
         <v>46213</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6963,7 +6963,7 @@
         <v>45649</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -7079,7 +7079,7 @@
         <v>44545</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -7186,7 +7186,7 @@
         <v>45748</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -7293,7 +7293,7 @@
         <v>45134</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -7400,7 +7400,7 @@
         <v>46013</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7512,7 +7512,7 @@
         <v>45012</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7619,7 +7619,7 @@
         <v>44825</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7735,7 +7735,7 @@
         <v>44810</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7845,7 +7845,7 @@
         <v>44726</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7956,7 +7956,7 @@
         <v>44824</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -8067,7 +8067,7 @@
         <v>45891</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -8178,7 +8178,7 @@
         <v>45891</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -8293,7 +8293,7 @@
         <v>45897</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -8404,7 +8404,7 @@
         <v>45951</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8515,7 +8515,7 @@
         <v>45992</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8626,7 +8626,7 @@
         <v>46178</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8737,7 +8737,7 @@
         <v>46184</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8848,7 +8848,7 @@
         <v>46184</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8959,7 +8959,7 @@
         <v>46213</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -9070,7 +9070,7 @@
         <v>46184</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -9181,7 +9181,7 @@
         <v>46300</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -9291,7 +9291,7 @@
         <v>46302</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -9406,7 +9406,7 @@
         <v>46261</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -9516,7 +9516,7 @@
         <v>45113</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9627,7 +9627,7 @@
         <v>45035</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9738,7 +9738,7 @@
         <v>45225</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9848,7 +9848,7 @@
         <v>45222</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9953,7 +9953,7 @@
         <v>45919</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -10063,7 +10063,7 @@
         <v>45799</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -10177,7 +10177,7 @@
         <v>45944</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -10287,7 +10287,7 @@
         <v>45819</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -10397,7 +10397,7 @@
         <v>45826</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -10507,7 +10507,7 @@
         <v>45951</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -10617,7 +10617,7 @@
         <v>45958</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10727,7 +10727,7 @@
         <v>44545</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10832,7 +10832,7 @@
         <v>45838</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10942,7 +10942,7 @@
         <v>45974</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -11052,7 +11052,7 @@
         <v>45974</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -11162,7 +11162,7 @@
         <v>45876</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -11272,7 +11272,7 @@
         <v>45982</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -11386,7 +11386,7 @@
         <v>45672</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -11496,7 +11496,7 @@
         <v>45985</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -11606,7 +11606,7 @@
         <v>44865</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11720,7 +11720,7 @@
         <v>46027</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11825,7 +11825,7 @@
         <v>46137</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11935,7 +11935,7 @@
         <v>45572</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -12045,7 +12045,7 @@
         <v>45608</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -12155,7 +12155,7 @@
         <v>45600</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -12260,7 +12260,7 @@
         <v>46197</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -12370,7 +12370,7 @@
         <v>46199</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -12480,7 +12480,7 @@
         <v>46199</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -12590,7 +12590,7 @@
         <v>45915</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -12700,7 +12700,7 @@
         <v>46276</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -12810,7 +12810,7 @@
         <v>46240</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -12920,7 +12920,7 @@
         <v>45918</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -13025,7 +13025,7 @@
         <v>46272</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -13135,7 +13135,7 @@
         <v>44967</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -13245,7 +13245,7 @@
         <v>45358</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -13350,7 +13350,7 @@
         <v>44820</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -13428,7 +13428,7 @@
         <v>44676</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -13501,7 +13501,7 @@
         <v>44543</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -13579,7 +13579,7 @@
         <v>44543</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -13657,7 +13657,7 @@
         <v>44543</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -13730,7 +13730,7 @@
         <v>44586</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -13808,7 +13808,7 @@
         <v>44586</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -13886,7 +13886,7 @@
         <v>44663</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -13959,7 +13959,7 @@
         <v>44685</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -14037,7 +14037,7 @@
         <v>44543</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -14115,7 +14115,7 @@
         <v>44824</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -14193,7 +14193,7 @@
         <v>44539</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -14271,7 +14271,7 @@
         <v>44743</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -14349,7 +14349,7 @@
         <v>44543</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -14427,7 +14427,7 @@
         <v>44586</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -14505,7 +14505,7 @@
         <v>44543</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -14583,7 +14583,7 @@
         <v>44573</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -14661,7 +14661,7 @@
         <v>44638</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -14739,7 +14739,7 @@
         <v>44820</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -14817,7 +14817,7 @@
         <v>44862</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -14890,7 +14890,7 @@
         <v>44532</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -14963,7 +14963,7 @@
         <v>44868</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -15041,7 +15041,7 @@
         <v>44841</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -15119,7 +15119,7 @@
         <v>45022</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -15197,7 +15197,7 @@
         <v>45090</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -15270,7 +15270,7 @@
         <v>45086</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -15343,7 +15343,7 @@
         <v>45482</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -15416,7 +15416,7 @@
         <v>45679</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -15494,7 +15494,7 @@
         <v>45534</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -15572,7 +15572,7 @@
         <v>44873</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -15650,7 +15650,7 @@
         <v>45474</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -15728,7 +15728,7 @@
         <v>45113</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -15806,7 +15806,7 @@
         <v>45106</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -15884,7 +15884,7 @@
         <v>44868</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -15957,7 +15957,7 @@
         <v>44866</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -16035,7 +16035,7 @@
         <v>44841</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -16113,7 +16113,7 @@
         <v>45397</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -16191,7 +16191,7 @@
         <v>45474</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -16269,7 +16269,7 @@
         <v>45474</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -16347,7 +16347,7 @@
         <v>45474</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -16425,7 +16425,7 @@
         <v>45474</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -16503,7 +16503,7 @@
         <v>45474</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -16581,7 +16581,7 @@
         <v>44589</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -16654,7 +16654,7 @@
         <v>45471</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -16732,7 +16732,7 @@
         <v>45463</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -16810,7 +16810,7 @@
         <v>45482</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -16883,7 +16883,7 @@
         <v>45884</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -16961,7 +16961,7 @@
         <v>45555</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -17039,7 +17039,7 @@
         <v>45883</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -17117,7 +17117,7 @@
         <v>45078</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -17195,7 +17195,7 @@
         <v>44966</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -17268,7 +17268,7 @@
         <v>44493</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -17346,7 +17346,7 @@
         <v>45505</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -17424,7 +17424,7 @@
         <v>45897</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -17502,7 +17502,7 @@
         <v>45490</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -17575,7 +17575,7 @@
         <v>45222</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -17648,7 +17648,7 @@
         <v>45901</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -17726,7 +17726,7 @@
         <v>44841</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -17804,7 +17804,7 @@
         <v>45124</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -17882,7 +17882,7 @@
         <v>45216</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -17960,7 +17960,7 @@
         <v>45093</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -18038,7 +18038,7 @@
         <v>45904</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -18116,7 +18116,7 @@
         <v>44984</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -18194,7 +18194,7 @@
         <v>45490</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -18267,7 +18267,7 @@
         <v>45490</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -18340,7 +18340,7 @@
         <v>45490</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -18413,7 +18413,7 @@
         <v>45490</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -18486,7 +18486,7 @@
         <v>45907</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -18559,7 +18559,7 @@
         <v>45073</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -18637,7 +18637,7 @@
         <v>45912</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -18715,7 +18715,7 @@
         <v>45491</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -18788,7 +18788,7 @@
         <v>45646</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -18861,7 +18861,7 @@
         <v>44539</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -18939,7 +18939,7 @@
         <v>45558</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -19017,7 +19017,7 @@
         <v>45166</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -19090,7 +19090,7 @@
         <v>45918</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -19168,7 +19168,7 @@
         <v>45664</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -19246,7 +19246,7 @@
         <v>44984</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -19324,7 +19324,7 @@
         <v>44984</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -19402,7 +19402,7 @@
         <v>44984</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -19480,7 +19480,7 @@
         <v>44984</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -19553,7 +19553,7 @@
         <v>44984</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -19631,7 +19631,7 @@
         <v>45491</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -19704,7 +19704,7 @@
         <v>45451</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -19782,7 +19782,7 @@
         <v>45124</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -19860,7 +19860,7 @@
         <v>45572</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -19938,7 +19938,7 @@
         <v>45028</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -20011,7 +20011,7 @@
         <v>45678</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -20089,7 +20089,7 @@
         <v>45928</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -20167,7 +20167,7 @@
         <v>45565</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -20240,7 +20240,7 @@
         <v>45887</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -20318,7 +20318,7 @@
         <v>44984</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -20396,7 +20396,7 @@
         <v>44984</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -20474,7 +20474,7 @@
         <v>45224</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -20552,7 +20552,7 @@
         <v>44984</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -20625,7 +20625,7 @@
         <v>44984</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -20698,7 +20698,7 @@
         <v>45526</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -20771,7 +20771,7 @@
         <v>45586</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -20844,7 +20844,7 @@
         <v>45555</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -20917,7 +20917,7 @@
         <v>45349</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -20990,7 +20990,7 @@
         <v>45259</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -21068,7 +21068,7 @@
         <v>45596</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -21146,7 +21146,7 @@
         <v>45544</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -21224,7 +21224,7 @@
         <v>45532</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -21297,7 +21297,7 @@
         <v>45590</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -21375,7 +21375,7 @@
         <v>45596</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -21453,7 +21453,7 @@
         <v>45940</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -21531,7 +21531,7 @@
         <v>45943</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -21609,7 +21609,7 @@
         <v>45942</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -21687,7 +21687,7 @@
         <v>45942</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -21765,7 +21765,7 @@
         <v>45604</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -21843,7 +21843,7 @@
         <v>45813</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -21916,7 +21916,7 @@
         <v>45946</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -21994,7 +21994,7 @@
         <v>45590</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -22072,7 +22072,7 @@
         <v>45950</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -22145,7 +22145,7 @@
         <v>45950</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -22218,7 +22218,7 @@
         <v>45819</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -22296,7 +22296,7 @@
         <v>45824</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -22369,7 +22369,7 @@
         <v>45826</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -22447,7 +22447,7 @@
         <v>45951</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -22525,7 +22525,7 @@
         <v>45951</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -22603,7 +22603,7 @@
         <v>45565</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -22681,7 +22681,7 @@
         <v>45827</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -22759,7 +22759,7 @@
         <v>45951</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -22837,7 +22837,7 @@
         <v>45951</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -22915,7 +22915,7 @@
         <v>44984</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -22993,7 +22993,7 @@
         <v>45951</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -23071,7 +23071,7 @@
         <v>45951</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -23149,7 +23149,7 @@
         <v>45951</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -23227,7 +23227,7 @@
         <v>45953</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -23305,7 +23305,7 @@
         <v>45953</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -23383,7 +23383,7 @@
         <v>45953</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -23461,7 +23461,7 @@
         <v>45953</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -23539,7 +23539,7 @@
         <v>45960</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -23612,7 +23612,7 @@
         <v>45111</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -23685,7 +23685,7 @@
         <v>45964</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -23763,7 +23763,7 @@
         <v>45965</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -23841,7 +23841,7 @@
         <v>45838</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -23919,7 +23919,7 @@
         <v>45965</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -23997,7 +23997,7 @@
         <v>45968</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -24070,7 +24070,7 @@
         <v>44802</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -24143,7 +24143,7 @@
         <v>45967</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -24216,7 +24216,7 @@
         <v>44851</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -24289,7 +24289,7 @@
         <v>45972</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -24367,7 +24367,7 @@
         <v>45971</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -24445,7 +24445,7 @@
         <v>45974</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -24523,7 +24523,7 @@
         <v>45973</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -24601,7 +24601,7 @@
         <v>45974</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -24679,7 +24679,7 @@
         <v>45973</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -24757,7 +24757,7 @@
         <v>45974</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -24835,7 +24835,7 @@
         <v>45974</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -24913,7 +24913,7 @@
         <v>45974</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -24991,7 +24991,7 @@
         <v>45974</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -25069,7 +25069,7 @@
         <v>45975</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -25142,7 +25142,7 @@
         <v>45124</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -25220,7 +25220,7 @@
         <v>45257</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -25298,7 +25298,7 @@
         <v>45488</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -25371,7 +25371,7 @@
         <v>45807</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -25449,7 +25449,7 @@
         <v>45868</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -25522,7 +25522,7 @@
         <v>45975</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -25600,7 +25600,7 @@
         <v>45028</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -25673,7 +25673,7 @@
         <v>45979</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -25751,7 +25751,7 @@
         <v>45474</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -25829,7 +25829,7 @@
         <v>45979</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -25907,7 +25907,7 @@
         <v>45763</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -25985,7 +25985,7 @@
         <v>45880</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -26063,7 +26063,7 @@
         <v>45985</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -26141,7 +26141,7 @@
         <v>45985</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -26219,7 +26219,7 @@
         <v>45043</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -26297,7 +26297,7 @@
         <v>45973</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -26375,7 +26375,7 @@
         <v>44984</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -26453,7 +26453,7 @@
         <v>46106</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -26531,7 +26531,7 @@
         <v>46106</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -26609,7 +26609,7 @@
         <v>46106</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -26687,7 +26687,7 @@
         <v>46108</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -26765,7 +26765,7 @@
         <v>46108</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -26843,7 +26843,7 @@
         <v>45516</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -26921,7 +26921,7 @@
         <v>45721</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -26994,7 +26994,7 @@
         <v>46108</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -27072,7 +27072,7 @@
         <v>44889</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -27150,7 +27150,7 @@
         <v>46113</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -27228,7 +27228,7 @@
         <v>44984</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -27306,7 +27306,7 @@
         <v>46113</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -27384,7 +27384,7 @@
         <v>46113</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -27462,7 +27462,7 @@
         <v>46113</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -27540,7 +27540,7 @@
         <v>46113</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -27618,7 +27618,7 @@
         <v>46113</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -27696,7 +27696,7 @@
         <v>44841</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -27774,7 +27774,7 @@
         <v>46114</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -27852,7 +27852,7 @@
         <v>45993</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -27930,7 +27930,7 @@
         <v>45994</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -28008,7 +28008,7 @@
         <v>45572</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -28086,7 +28086,7 @@
         <v>45995</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -28164,7 +28164,7 @@
         <v>45995</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -28242,7 +28242,7 @@
         <v>45517</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -28320,7 +28320,7 @@
         <v>45576</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -28398,7 +28398,7 @@
         <v>45953</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -28476,7 +28476,7 @@
         <v>44966</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -28554,7 +28554,7 @@
         <v>46010</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -28627,7 +28627,7 @@
         <v>45113</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -28705,7 +28705,7 @@
         <v>46006</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -28778,7 +28778,7 @@
         <v>45073</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -28856,7 +28856,7 @@
         <v>45323</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -28929,7 +28929,7 @@
         <v>46010</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -29002,7 +29002,7 @@
         <v>45028</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -29075,7 +29075,7 @@
         <v>45572</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -29153,7 +29153,7 @@
         <v>45596</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -29231,7 +29231,7 @@
         <v>46021</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -29304,7 +29304,7 @@
         <v>46010</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -29377,7 +29377,7 @@
         <v>46010</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -29455,7 +29455,7 @@
         <v>46009</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -29528,7 +29528,7 @@
         <v>46030</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -29606,7 +29606,7 @@
         <v>45994</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -29684,7 +29684,7 @@
         <v>45057</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -29762,7 +29762,7 @@
         <v>46137</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -29840,7 +29840,7 @@
         <v>45113</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -29918,7 +29918,7 @@
         <v>45992</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -29996,7 +29996,7 @@
         <v>45993</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -30074,7 +30074,7 @@
         <v>45693</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -30147,7 +30147,7 @@
         <v>45544</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -30225,7 +30225,7 @@
         <v>45677</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -30303,7 +30303,7 @@
         <v>45168</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -30381,7 +30381,7 @@
         <v>45904</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -30454,7 +30454,7 @@
         <v>45883</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -30532,7 +30532,7 @@
         <v>45572</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -30610,7 +30610,7 @@
         <v>45608</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -30683,7 +30683,7 @@
         <v>46077</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -30761,7 +30761,7 @@
         <v>46077</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -30839,7 +30839,7 @@
         <v>46077</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -30917,7 +30917,7 @@
         <v>46077</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -30995,7 +30995,7 @@
         <v>45903</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -31073,7 +31073,7 @@
         <v>46083</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -31146,7 +31146,7 @@
         <v>46092</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -31224,7 +31224,7 @@
         <v>46092</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -31302,7 +31302,7 @@
         <v>45842</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -31380,7 +31380,7 @@
         <v>46092</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -31458,7 +31458,7 @@
         <v>46092</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -31536,7 +31536,7 @@
         <v>46162</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -31614,7 +31614,7 @@
         <v>46164</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -31692,7 +31692,7 @@
         <v>45860</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -31765,7 +31765,7 @@
         <v>45824</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -31838,7 +31838,7 @@
         <v>45883</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -31916,7 +31916,7 @@
         <v>46170</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -31994,7 +31994,7 @@
         <v>46170</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -32067,7 +32067,7 @@
         <v>46177</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -32145,7 +32145,7 @@
         <v>46177</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -32223,7 +32223,7 @@
         <v>46177</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -32301,7 +32301,7 @@
         <v>46177</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -32379,7 +32379,7 @@
         <v>46178</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -32457,7 +32457,7 @@
         <v>46183</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -32535,7 +32535,7 @@
         <v>46185</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -32613,7 +32613,7 @@
         <v>46191</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -32691,7 +32691,7 @@
         <v>46192</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -32769,7 +32769,7 @@
         <v>46191</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -32847,7 +32847,7 @@
         <v>45613</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -32920,7 +32920,7 @@
         <v>46197</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -32998,7 +32998,7 @@
         <v>46197</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -33076,7 +33076,7 @@
         <v>46197</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -33154,7 +33154,7 @@
         <v>45986</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -33227,7 +33227,7 @@
         <v>46199</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -33305,7 +33305,7 @@
         <v>46199</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -33383,7 +33383,7 @@
         <v>46199</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -33461,7 +33461,7 @@
         <v>46198</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -33534,7 +33534,7 @@
         <v>46205</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -33607,7 +33607,7 @@
         <v>46204</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -33685,7 +33685,7 @@
         <v>46205</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -33758,7 +33758,7 @@
         <v>46206</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -33831,7 +33831,7 @@
         <v>46206</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -33904,7 +33904,7 @@
         <v>46211</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -33982,7 +33982,7 @@
         <v>46215</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -34055,7 +34055,7 @@
         <v>46215</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -34128,7 +34128,7 @@
         <v>46212</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -34206,7 +34206,7 @@
         <v>46212</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -34284,7 +34284,7 @@
         <v>45520</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -34362,7 +34362,7 @@
         <v>46216</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -34435,7 +34435,7 @@
         <v>46175</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -34508,7 +34508,7 @@
         <v>46216</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -34581,7 +34581,7 @@
         <v>46266</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -34659,7 +34659,7 @@
         <v>46274</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -34737,7 +34737,7 @@
         <v>46009</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -34810,7 +34810,7 @@
         <v>46237</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -34883,7 +34883,7 @@
         <v>44841</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -34961,7 +34961,7 @@
         <v>46281</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -35039,7 +35039,7 @@
         <v>46281</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -35117,7 +35117,7 @@
         <v>46281</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -35195,7 +35195,7 @@
         <v>46281</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -35273,7 +35273,7 @@
         <v>46238</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -35351,7 +35351,7 @@
         <v>46281</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -35429,7 +35429,7 @@
         <v>46288</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -35507,7 +35507,7 @@
         <v>46077</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -35580,7 +35580,7 @@
         <v>44854</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -35658,7 +35658,7 @@
         <v>46289</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -35736,7 +35736,7 @@
         <v>46170</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -35809,7 +35809,7 @@
         <v>46174</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -35887,7 +35887,7 @@
         <v>46247</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -35960,7 +35960,7 @@
         <v>46248</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -36033,7 +36033,7 @@
         <v>46248</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -36106,7 +36106,7 @@
         <v>46294</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -36184,7 +36184,7 @@
         <v>46253</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -36257,7 +36257,7 @@
         <v>46255</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -36330,7 +36330,7 @@
         <v>46300</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -36408,7 +36408,7 @@
         <v>46300</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -36486,7 +36486,7 @@
         <v>46300</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -36564,7 +36564,7 @@
         <v>46300</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -36642,7 +36642,7 @@
         <v>46295</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -36720,7 +36720,7 @@
         <v>46300</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -36798,7 +36798,7 @@
         <v>46254</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -36876,7 +36876,7 @@
         <v>46301</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -36954,7 +36954,7 @@
         <v>46301</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -37032,7 +37032,7 @@
         <v>46303</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -37110,7 +37110,7 @@
         <v>46304</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -37188,7 +37188,7 @@
         <v>44823</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -37266,7 +37266,7 @@
         <v>44820</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -37339,7 +37339,7 @@
         <v>45392</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -37412,7 +37412,7 @@
         <v>44823</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -37490,7 +37490,7 @@
         <v>45327</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -37563,7 +37563,7 @@
         <v>45327</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -37636,7 +37636,7 @@
         <v>44824</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -37714,7 +37714,7 @@
         <v>45756</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -37787,7 +37787,7 @@
         <v>45841</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -37865,7 +37865,7 @@
         <v>46147</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -37938,7 +37938,7 @@
         <v>46147</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -38011,7 +38011,7 @@
         <v>46147</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -38084,7 +38084,7 @@
         <v>46148</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -38157,7 +38157,7 @@
         <v>46148</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>

--- a/Översikt JOKKMOKK.xlsx
+++ b/Översikt JOKKMOKK.xlsx
@@ -601,7 +601,7 @@
         <v>45680</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -766,7 +766,7 @@
         <v>45971</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -918,7 +918,7 @@
         <v>46230</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1067,7 +1067,7 @@
         <v>46043</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1205,7 +1205,7 @@
         <v>46184</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1346,7 +1346,7 @@
         <v>46177</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1486,7 +1486,7 @@
         <v>44917</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1624,7 +1624,7 @@
         <v>44539</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1760,7 +1760,7 @@
         <v>46244</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1896,7 +1896,7 @@
         <v>44824</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>45222</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2165,7 +2165,7 @@
         <v>46010</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2293,7 +2293,7 @@
         <v>45672</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2425,7 +2425,7 @@
         <v>44781</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2552,7 +2552,7 @@
         <v>45476</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2679,7 +2679,7 @@
         <v>45805</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2811,7 +2811,7 @@
         <v>45237</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2942,7 +2942,7 @@
         <v>45985</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -3069,7 +3069,7 @@
         <v>45649</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3198,7 +3198,7 @@
         <v>45993</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3322,7 +3322,7 @@
         <v>44722</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3445,7 +3445,7 @@
         <v>45174</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3572,7 +3572,7 @@
         <v>45484</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3699,7 +3699,7 @@
         <v>45672</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3826,7 +3826,7 @@
         <v>45649</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3950,7 +3950,7 @@
         <v>44552</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -4069,7 +4069,7 @@
         <v>45596</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -4192,7 +4192,7 @@
         <v>45986</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4311,7 +4311,7 @@
         <v>45994</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4430,7 +4430,7 @@
         <v>46184</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4553,7 +4553,7 @@
         <v>45476</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4671,7 +4671,7 @@
         <v>45810</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4788,7 +4788,7 @@
         <v>45113</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4906,7 +4906,7 @@
         <v>46283</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -5028,7 +5028,7 @@
         <v>46042</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -5149,7 +5149,7 @@
         <v>45940</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -5265,7 +5265,7 @@
         <v>46184</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5381,7 +5381,7 @@
         <v>46101</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5496,7 +5496,7 @@
         <v>44722</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5611,7 +5611,7 @@
         <v>46149</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5721,7 +5721,7 @@
         <v>44490</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5835,7 +5835,7 @@
         <v>45609</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5953,7 +5953,7 @@
         <v>46184</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -6067,7 +6067,7 @@
         <v>45484</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -6181,7 +6181,7 @@
         <v>46300</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -6295,7 +6295,7 @@
         <v>46090</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6404,7 +6404,7 @@
         <v>45114</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6517,7 +6517,7 @@
         <v>45170</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6630,7 +6630,7 @@
         <v>46113</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6743,7 +6743,7 @@
         <v>46206</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6851,7 +6851,7 @@
         <v>46213</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6963,7 +6963,7 @@
         <v>45748</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -7070,7 +7070,7 @@
         <v>45134</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -7177,7 +7177,7 @@
         <v>45649</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -7293,7 +7293,7 @@
         <v>46013</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -7405,7 +7405,7 @@
         <v>44545</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7512,7 +7512,7 @@
         <v>45012</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7619,7 +7619,7 @@
         <v>44825</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7735,7 +7735,7 @@
         <v>44810</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7845,7 +7845,7 @@
         <v>44726</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7956,7 +7956,7 @@
         <v>44824</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -8067,7 +8067,7 @@
         <v>45891</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -8178,7 +8178,7 @@
         <v>45891</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -8293,7 +8293,7 @@
         <v>45897</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -8404,7 +8404,7 @@
         <v>45951</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8515,7 +8515,7 @@
         <v>45992</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8626,7 +8626,7 @@
         <v>46178</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8737,7 +8737,7 @@
         <v>46184</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8848,7 +8848,7 @@
         <v>46184</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8959,7 +8959,7 @@
         <v>46213</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -9070,7 +9070,7 @@
         <v>46184</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -9181,7 +9181,7 @@
         <v>46300</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -9291,7 +9291,7 @@
         <v>46302</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -9406,7 +9406,7 @@
         <v>46261</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -9516,7 +9516,7 @@
         <v>45113</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9627,7 +9627,7 @@
         <v>45035</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9738,7 +9738,7 @@
         <v>44545</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9843,7 +9843,7 @@
         <v>46137</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9953,7 +9953,7 @@
         <v>45919</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -10063,7 +10063,7 @@
         <v>45944</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -10173,7 +10173,7 @@
         <v>45951</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -10283,7 +10283,7 @@
         <v>45958</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -10393,7 +10393,7 @@
         <v>45974</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -10503,7 +10503,7 @@
         <v>45974</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -10613,7 +10613,7 @@
         <v>45225</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10723,7 +10723,7 @@
         <v>45672</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10833,7 +10833,7 @@
         <v>45982</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10947,7 +10947,7 @@
         <v>45985</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -11057,7 +11057,7 @@
         <v>45608</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -11167,7 +11167,7 @@
         <v>46027</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -11272,7 +11272,7 @@
         <v>45572</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -11382,7 +11382,7 @@
         <v>45600</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -11487,7 +11487,7 @@
         <v>46197</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -11597,7 +11597,7 @@
         <v>46199</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11707,7 +11707,7 @@
         <v>46199</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11817,7 +11817,7 @@
         <v>45222</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11922,7 +11922,7 @@
         <v>44865</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -12036,7 +12036,7 @@
         <v>45915</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -12146,7 +12146,7 @@
         <v>46276</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -12256,7 +12256,7 @@
         <v>46240</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -12366,7 +12366,7 @@
         <v>45918</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -12471,7 +12471,7 @@
         <v>46272</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -12581,7 +12581,7 @@
         <v>45799</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -12695,7 +12695,7 @@
         <v>45819</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -12805,7 +12805,7 @@
         <v>45826</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -12915,7 +12915,7 @@
         <v>45838</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -13025,7 +13025,7 @@
         <v>45876</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -13135,7 +13135,7 @@
         <v>44967</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -13245,7 +13245,7 @@
         <v>45358</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -13350,7 +13350,7 @@
         <v>44820</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -13428,7 +13428,7 @@
         <v>44676</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -13501,7 +13501,7 @@
         <v>44543</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -13579,7 +13579,7 @@
         <v>44543</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -13657,7 +13657,7 @@
         <v>44543</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -13730,7 +13730,7 @@
         <v>44586</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -13808,7 +13808,7 @@
         <v>44586</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -13886,7 +13886,7 @@
         <v>44663</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -13959,7 +13959,7 @@
         <v>44685</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -14037,7 +14037,7 @@
         <v>44539</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -14115,7 +14115,7 @@
         <v>44543</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -14193,7 +14193,7 @@
         <v>44543</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -14271,7 +14271,7 @@
         <v>44638</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -14349,7 +14349,7 @@
         <v>44743</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -14427,7 +14427,7 @@
         <v>44543</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -14505,7 +14505,7 @@
         <v>44586</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -14583,7 +14583,7 @@
         <v>44573</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -14661,7 +14661,7 @@
         <v>44820</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -14739,7 +14739,7 @@
         <v>44824</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -14817,7 +14817,7 @@
         <v>44532</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -14890,7 +14890,7 @@
         <v>44868</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -14968,7 +14968,7 @@
         <v>45028</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -15041,7 +15041,7 @@
         <v>44966</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -15114,7 +15114,7 @@
         <v>45106</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -15192,7 +15192,7 @@
         <v>44841</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -15270,7 +15270,7 @@
         <v>44539</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -15348,7 +15348,7 @@
         <v>45586</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -15421,7 +15421,7 @@
         <v>45596</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -15499,7 +15499,7 @@
         <v>45491</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -15572,7 +15572,7 @@
         <v>45482</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -15645,7 +15645,7 @@
         <v>45463</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -15723,7 +15723,7 @@
         <v>45222</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -15796,7 +15796,7 @@
         <v>45558</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -15874,7 +15874,7 @@
         <v>45086</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -15947,7 +15947,7 @@
         <v>45482</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -16020,7 +16020,7 @@
         <v>45677</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -16098,7 +16098,7 @@
         <v>45349</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -16171,7 +16171,7 @@
         <v>45572</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -16249,7 +16249,7 @@
         <v>44984</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -16322,7 +16322,7 @@
         <v>44984</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -16395,7 +16395,7 @@
         <v>45124</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -16473,7 +16473,7 @@
         <v>44984</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -16551,7 +16551,7 @@
         <v>44984</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -16629,7 +16629,7 @@
         <v>44984</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -16707,7 +16707,7 @@
         <v>45664</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -16785,7 +16785,7 @@
         <v>45679</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -16863,7 +16863,7 @@
         <v>44862</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -16936,7 +16936,7 @@
         <v>44873</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -17014,7 +17014,7 @@
         <v>45257</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -17092,7 +17092,7 @@
         <v>45488</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -17165,7 +17165,7 @@
         <v>45323</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -17238,7 +17238,7 @@
         <v>45124</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -17316,7 +17316,7 @@
         <v>45646</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -17389,7 +17389,7 @@
         <v>45043</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -17467,7 +17467,7 @@
         <v>45516</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -17545,7 +17545,7 @@
         <v>45517</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -17623,7 +17623,7 @@
         <v>44889</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -17701,7 +17701,7 @@
         <v>45596</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -17779,7 +17779,7 @@
         <v>44841</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -17857,7 +17857,7 @@
         <v>44966</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -17935,7 +17935,7 @@
         <v>45884</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -18013,7 +18013,7 @@
         <v>45897</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -18091,7 +18091,7 @@
         <v>46137</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -18169,7 +18169,7 @@
         <v>45474</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -18247,7 +18247,7 @@
         <v>45474</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -18325,7 +18325,7 @@
         <v>45474</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -18403,7 +18403,7 @@
         <v>45904</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -18476,7 +18476,7 @@
         <v>45901</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -18554,7 +18554,7 @@
         <v>45904</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -18632,7 +18632,7 @@
         <v>45491</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -18705,7 +18705,7 @@
         <v>45907</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -18778,7 +18778,7 @@
         <v>45912</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -18856,7 +18856,7 @@
         <v>45918</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -18934,7 +18934,7 @@
         <v>44493</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -19012,7 +19012,7 @@
         <v>45887</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -19090,7 +19090,7 @@
         <v>45928</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -19168,7 +19168,7 @@
         <v>45608</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -19241,7 +19241,7 @@
         <v>45216</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -19319,7 +19319,7 @@
         <v>45028</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -19392,7 +19392,7 @@
         <v>45942</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -19470,7 +19470,7 @@
         <v>45942</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -19548,7 +19548,7 @@
         <v>45943</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -19626,7 +19626,7 @@
         <v>45940</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -19704,7 +19704,7 @@
         <v>45946</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -19782,7 +19782,7 @@
         <v>45951</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -19860,7 +19860,7 @@
         <v>46083</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -19933,7 +19933,7 @@
         <v>45951</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -20011,7 +20011,7 @@
         <v>45951</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -20089,7 +20089,7 @@
         <v>45951</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -20167,7 +20167,7 @@
         <v>45951</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -20245,7 +20245,7 @@
         <v>45951</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -20323,7 +20323,7 @@
         <v>45951</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -20401,7 +20401,7 @@
         <v>45950</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -20474,7 +20474,7 @@
         <v>45950</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -20547,7 +20547,7 @@
         <v>45953</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -20625,7 +20625,7 @@
         <v>44984</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -20703,7 +20703,7 @@
         <v>44984</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -20781,7 +20781,7 @@
         <v>45953</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -20859,7 +20859,7 @@
         <v>45953</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -20937,7 +20937,7 @@
         <v>45953</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -21015,7 +21015,7 @@
         <v>45903</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -21093,7 +21093,7 @@
         <v>44589</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -21166,7 +21166,7 @@
         <v>45960</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -21239,7 +21239,7 @@
         <v>45168</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -21317,7 +21317,7 @@
         <v>45965</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -21395,7 +21395,7 @@
         <v>45842</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -21473,7 +21473,7 @@
         <v>45964</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -21551,7 +21551,7 @@
         <v>45965</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -21629,7 +21629,7 @@
         <v>45967</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -21702,7 +21702,7 @@
         <v>45971</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -21780,7 +21780,7 @@
         <v>45968</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -21853,7 +21853,7 @@
         <v>45973</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -21931,7 +21931,7 @@
         <v>45973</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -22009,7 +22009,7 @@
         <v>45111</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -22082,7 +22082,7 @@
         <v>45972</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -22160,7 +22160,7 @@
         <v>45975</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -22238,7 +22238,7 @@
         <v>45974</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -22316,7 +22316,7 @@
         <v>45974</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -22394,7 +22394,7 @@
         <v>45824</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -22467,7 +22467,7 @@
         <v>45974</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -22545,7 +22545,7 @@
         <v>45974</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -22623,7 +22623,7 @@
         <v>45166</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -22696,7 +22696,7 @@
         <v>46162</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -22774,7 +22774,7 @@
         <v>45974</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -22852,7 +22852,7 @@
         <v>45975</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -22925,7 +22925,7 @@
         <v>45974</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -23003,7 +23003,7 @@
         <v>45979</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -23081,7 +23081,7 @@
         <v>45979</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -23159,7 +23159,7 @@
         <v>46164</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -23237,7 +23237,7 @@
         <v>45985</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -23315,7 +23315,7 @@
         <v>45985</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -23393,7 +23393,7 @@
         <v>45860</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -23466,7 +23466,7 @@
         <v>45721</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -23539,7 +23539,7 @@
         <v>45883</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -23617,7 +23617,7 @@
         <v>45973</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -23695,7 +23695,7 @@
         <v>45073</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -23773,7 +23773,7 @@
         <v>45995</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -23851,7 +23851,7 @@
         <v>45995</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -23929,7 +23929,7 @@
         <v>45113</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -24007,7 +24007,7 @@
         <v>45994</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -24085,7 +24085,7 @@
         <v>45953</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -24163,7 +24163,7 @@
         <v>46170</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -24241,7 +24241,7 @@
         <v>46170</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -24314,7 +24314,7 @@
         <v>46006</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -24387,7 +24387,7 @@
         <v>45474</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -24465,7 +24465,7 @@
         <v>45474</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -24543,7 +24543,7 @@
         <v>45397</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -24621,7 +24621,7 @@
         <v>46010</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -24694,7 +24694,7 @@
         <v>44868</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -24767,7 +24767,7 @@
         <v>45572</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -24845,7 +24845,7 @@
         <v>46021</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -24918,7 +24918,7 @@
         <v>46010</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -24991,7 +24991,7 @@
         <v>46010</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -25069,7 +25069,7 @@
         <v>46009</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -25142,7 +25142,7 @@
         <v>45993</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -25220,7 +25220,7 @@
         <v>45992</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -25298,7 +25298,7 @@
         <v>45994</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -25376,7 +25376,7 @@
         <v>46030</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -25454,7 +25454,7 @@
         <v>46177</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -25532,7 +25532,7 @@
         <v>45693</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -25605,7 +25605,7 @@
         <v>46177</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -25683,7 +25683,7 @@
         <v>46178</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -25761,7 +25761,7 @@
         <v>46177</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -25839,7 +25839,7 @@
         <v>45544</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -25917,7 +25917,7 @@
         <v>46177</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -25995,7 +25995,7 @@
         <v>45604</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -26073,7 +26073,7 @@
         <v>45678</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -26151,7 +26151,7 @@
         <v>45883</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -26229,7 +26229,7 @@
         <v>45090</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -26302,7 +26302,7 @@
         <v>45572</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -26380,7 +26380,7 @@
         <v>46183</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -26458,7 +26458,7 @@
         <v>45474</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -26536,7 +26536,7 @@
         <v>45526</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -26609,7 +26609,7 @@
         <v>44802</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -26682,7 +26682,7 @@
         <v>46077</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -26760,7 +26760,7 @@
         <v>46077</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -26838,7 +26838,7 @@
         <v>44851</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -26911,7 +26911,7 @@
         <v>46077</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -26989,7 +26989,7 @@
         <v>46077</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -27067,7 +27067,7 @@
         <v>45534</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -27145,7 +27145,7 @@
         <v>46185</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -27223,7 +27223,7 @@
         <v>46092</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -27301,7 +27301,7 @@
         <v>46092</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -27379,7 +27379,7 @@
         <v>46092</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -27457,7 +27457,7 @@
         <v>46092</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -27535,7 +27535,7 @@
         <v>46191</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -27613,7 +27613,7 @@
         <v>46191</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -27691,7 +27691,7 @@
         <v>46192</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -27769,7 +27769,7 @@
         <v>45113</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -27847,7 +27847,7 @@
         <v>46106</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -27925,7 +27925,7 @@
         <v>46106</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -28003,7 +28003,7 @@
         <v>46108</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -28081,7 +28081,7 @@
         <v>46198</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -28154,7 +28154,7 @@
         <v>46108</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -28232,7 +28232,7 @@
         <v>46108</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -28310,7 +28310,7 @@
         <v>45986</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -28383,7 +28383,7 @@
         <v>46106</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -28461,7 +28461,7 @@
         <v>45613</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -28534,7 +28534,7 @@
         <v>45763</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -28612,7 +28612,7 @@
         <v>45224</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -28690,7 +28690,7 @@
         <v>46113</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -28768,7 +28768,7 @@
         <v>46113</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -28846,7 +28846,7 @@
         <v>46113</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -28924,7 +28924,7 @@
         <v>46114</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -29002,7 +29002,7 @@
         <v>46113</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -29080,7 +29080,7 @@
         <v>46197</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -29158,7 +29158,7 @@
         <v>45474</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -29236,7 +29236,7 @@
         <v>46197</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -29314,7 +29314,7 @@
         <v>46197</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -29392,7 +29392,7 @@
         <v>46113</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -29470,7 +29470,7 @@
         <v>46113</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -29548,7 +29548,7 @@
         <v>45993</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -29626,7 +29626,7 @@
         <v>46199</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -29704,7 +29704,7 @@
         <v>45572</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -29782,7 +29782,7 @@
         <v>46199</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -29860,7 +29860,7 @@
         <v>46010</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -29933,7 +29933,7 @@
         <v>46199</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -30011,7 +30011,7 @@
         <v>45505</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -30089,7 +30089,7 @@
         <v>45565</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -30167,7 +30167,7 @@
         <v>45124</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -30245,7 +30245,7 @@
         <v>46204</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -30323,7 +30323,7 @@
         <v>45113</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -30401,7 +30401,7 @@
         <v>45555</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -30474,7 +30474,7 @@
         <v>46205</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -30547,7 +30547,7 @@
         <v>46206</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -30620,7 +30620,7 @@
         <v>46206</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -30693,7 +30693,7 @@
         <v>44866</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -30771,7 +30771,7 @@
         <v>45590</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -30849,7 +30849,7 @@
         <v>46205</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -30922,7 +30922,7 @@
         <v>46212</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -31000,7 +31000,7 @@
         <v>46211</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -31078,7 +31078,7 @@
         <v>46212</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -31156,7 +31156,7 @@
         <v>45520</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -31234,7 +31234,7 @@
         <v>46215</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -31307,7 +31307,7 @@
         <v>46216</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -31380,7 +31380,7 @@
         <v>46216</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -31453,7 +31453,7 @@
         <v>46215</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -31526,7 +31526,7 @@
         <v>45078</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -31604,7 +31604,7 @@
         <v>46175</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -31677,7 +31677,7 @@
         <v>45028</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -31750,7 +31750,7 @@
         <v>45093</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -31828,7 +31828,7 @@
         <v>46009</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -31901,7 +31901,7 @@
         <v>45471</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -31979,7 +31979,7 @@
         <v>44984</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -32057,7 +32057,7 @@
         <v>46274</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -32135,7 +32135,7 @@
         <v>44841</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -32213,7 +32213,7 @@
         <v>44841</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -32291,7 +32291,7 @@
         <v>44984</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -32369,7 +32369,7 @@
         <v>44984</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -32447,7 +32447,7 @@
         <v>44984</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -32525,7 +32525,7 @@
         <v>44984</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -32598,7 +32598,7 @@
         <v>44984</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -32676,7 +32676,7 @@
         <v>45490</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -32749,7 +32749,7 @@
         <v>46281</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -32827,7 +32827,7 @@
         <v>44841</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -32905,7 +32905,7 @@
         <v>46238</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -32983,7 +32983,7 @@
         <v>46281</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -33061,7 +33061,7 @@
         <v>45022</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -33139,7 +33139,7 @@
         <v>46281</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -33217,7 +33217,7 @@
         <v>46281</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -33295,7 +33295,7 @@
         <v>45576</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -33373,7 +33373,7 @@
         <v>46237</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -33446,7 +33446,7 @@
         <v>46281</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -33524,7 +33524,7 @@
         <v>46077</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -33597,7 +33597,7 @@
         <v>45555</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -33675,7 +33675,7 @@
         <v>46288</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -33753,7 +33753,7 @@
         <v>46289</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -33831,7 +33831,7 @@
         <v>45490</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -33904,7 +33904,7 @@
         <v>45490</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -33977,7 +33977,7 @@
         <v>45490</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -34050,7 +34050,7 @@
         <v>45490</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -34123,7 +34123,7 @@
         <v>46248</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -34196,7 +34196,7 @@
         <v>46170</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -34269,7 +34269,7 @@
         <v>44854</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -34347,7 +34347,7 @@
         <v>46247</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -34420,7 +34420,7 @@
         <v>46174</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -34498,7 +34498,7 @@
         <v>45057</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -34576,7 +34576,7 @@
         <v>45073</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -34654,7 +34654,7 @@
         <v>46253</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -34727,7 +34727,7 @@
         <v>45565</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -34800,7 +34800,7 @@
         <v>46294</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -34878,7 +34878,7 @@
         <v>46295</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -34956,7 +34956,7 @@
         <v>46254</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -35034,7 +35034,7 @@
         <v>46255</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -35107,7 +35107,7 @@
         <v>46301</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -35185,7 +35185,7 @@
         <v>46301</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -35263,7 +35263,7 @@
         <v>46300</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -35341,7 +35341,7 @@
         <v>46300</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -35419,7 +35419,7 @@
         <v>46300</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -35497,7 +35497,7 @@
         <v>46300</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -35575,7 +35575,7 @@
         <v>45451</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -35653,7 +35653,7 @@
         <v>46303</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -35731,7 +35731,7 @@
         <v>46300</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -35809,7 +35809,7 @@
         <v>46304</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -35887,7 +35887,7 @@
         <v>45544</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -35965,7 +35965,7 @@
         <v>45259</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -36043,7 +36043,7 @@
         <v>45596</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -36121,7 +36121,7 @@
         <v>46266</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -36199,7 +36199,7 @@
         <v>45532</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -36272,7 +36272,7 @@
         <v>46248</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -36345,7 +36345,7 @@
         <v>46310</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -36423,7 +36423,7 @@
         <v>45813</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -36496,7 +36496,7 @@
         <v>45590</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -36574,7 +36574,7 @@
         <v>45819</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -36652,7 +36652,7 @@
         <v>45824</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -36725,7 +36725,7 @@
         <v>45827</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -36803,7 +36803,7 @@
         <v>45826</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -36881,7 +36881,7 @@
         <v>45838</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -36959,7 +36959,7 @@
         <v>45868</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -37032,7 +37032,7 @@
         <v>45807</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -37110,7 +37110,7 @@
         <v>45880</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -37188,7 +37188,7 @@
         <v>45883</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -37266,7 +37266,7 @@
         <v>44823</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -37344,7 +37344,7 @@
         <v>44820</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -37417,7 +37417,7 @@
         <v>45392</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -37490,7 +37490,7 @@
         <v>44823</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -37568,7 +37568,7 @@
         <v>45327</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -37641,7 +37641,7 @@
         <v>45327</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -37714,7 +37714,7 @@
         <v>44824</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -37792,7 +37792,7 @@
         <v>45756</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -37865,7 +37865,7 @@
         <v>45841</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -37943,7 +37943,7 @@
         <v>46147</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -38016,7 +38016,7 @@
         <v>46147</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -38089,7 +38089,7 @@
         <v>46147</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -38162,7 +38162,7 @@
         <v>46148</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -38235,7 +38235,7 @@
         <v>46148</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>

--- a/Översikt JOKKMOKK.xlsx
+++ b/Översikt JOKKMOKK.xlsx
@@ -601,7 +601,7 @@
         <v>45680</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -766,7 +766,7 @@
         <v>45971</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -918,7 +918,7 @@
         <v>46230</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1067,7 +1067,7 @@
         <v>46043</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1205,7 +1205,7 @@
         <v>46184</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1346,7 +1346,7 @@
         <v>46177</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1486,7 +1486,7 @@
         <v>44917</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1624,7 +1624,7 @@
         <v>44539</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1760,7 +1760,7 @@
         <v>46244</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1896,7 +1896,7 @@
         <v>44824</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>45222</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2165,7 +2165,7 @@
         <v>46010</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2293,7 +2293,7 @@
         <v>45672</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2425,7 +2425,7 @@
         <v>44781</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2552,7 +2552,7 @@
         <v>45476</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2679,7 +2679,7 @@
         <v>45805</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2811,7 +2811,7 @@
         <v>45237</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2942,7 +2942,7 @@
         <v>45985</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -3069,7 +3069,7 @@
         <v>45649</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3198,7 +3198,7 @@
         <v>45993</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3322,7 +3322,7 @@
         <v>44722</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3445,7 +3445,7 @@
         <v>45174</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3572,7 +3572,7 @@
         <v>45484</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3699,7 +3699,7 @@
         <v>45672</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3826,7 +3826,7 @@
         <v>45649</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3950,7 +3950,7 @@
         <v>44552</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -4069,7 +4069,7 @@
         <v>45596</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -4192,7 +4192,7 @@
         <v>45986</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4311,7 +4311,7 @@
         <v>45994</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4430,7 +4430,7 @@
         <v>46184</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4553,7 +4553,7 @@
         <v>45476</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4671,7 +4671,7 @@
         <v>45810</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4788,7 +4788,7 @@
         <v>45113</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4906,7 +4906,7 @@
         <v>46283</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -5028,7 +5028,7 @@
         <v>46042</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -5149,7 +5149,7 @@
         <v>45940</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -5265,7 +5265,7 @@
         <v>46184</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5381,7 +5381,7 @@
         <v>46101</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5496,7 +5496,7 @@
         <v>44722</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5611,7 +5611,7 @@
         <v>46149</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5721,7 +5721,7 @@
         <v>44490</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5835,7 +5835,7 @@
         <v>45609</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5953,7 +5953,7 @@
         <v>46184</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -6067,7 +6067,7 @@
         <v>45484</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -6181,7 +6181,7 @@
         <v>46300</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -6295,7 +6295,7 @@
         <v>46090</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6404,7 +6404,7 @@
         <v>45114</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6517,7 +6517,7 @@
         <v>45170</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6630,7 +6630,7 @@
         <v>46113</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6743,7 +6743,7 @@
         <v>46206</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6851,7 +6851,7 @@
         <v>46213</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6963,7 +6963,7 @@
         <v>45748</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -7070,7 +7070,7 @@
         <v>45134</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -7177,7 +7177,7 @@
         <v>45649</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -7293,7 +7293,7 @@
         <v>46013</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -7405,7 +7405,7 @@
         <v>44545</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7512,7 +7512,7 @@
         <v>45012</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7619,7 +7619,7 @@
         <v>44825</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7735,7 +7735,7 @@
         <v>44810</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7845,7 +7845,7 @@
         <v>44726</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7956,7 +7956,7 @@
         <v>44824</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -8067,7 +8067,7 @@
         <v>45891</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -8178,7 +8178,7 @@
         <v>45891</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -8293,7 +8293,7 @@
         <v>45897</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -8404,7 +8404,7 @@
         <v>45951</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8515,7 +8515,7 @@
         <v>45992</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8626,7 +8626,7 @@
         <v>46178</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8737,7 +8737,7 @@
         <v>46184</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8848,7 +8848,7 @@
         <v>46184</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8959,7 +8959,7 @@
         <v>46213</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -9070,7 +9070,7 @@
         <v>46184</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -9181,7 +9181,7 @@
         <v>46300</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -9291,7 +9291,7 @@
         <v>46302</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -9406,7 +9406,7 @@
         <v>46261</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -9516,7 +9516,7 @@
         <v>45113</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9627,7 +9627,7 @@
         <v>45035</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9738,7 +9738,7 @@
         <v>44545</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9843,7 +9843,7 @@
         <v>46137</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9953,7 +9953,7 @@
         <v>45919</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -10063,7 +10063,7 @@
         <v>45944</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -10173,7 +10173,7 @@
         <v>45951</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -10283,7 +10283,7 @@
         <v>45958</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -10393,7 +10393,7 @@
         <v>45974</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -10503,7 +10503,7 @@
         <v>45974</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -10613,7 +10613,7 @@
         <v>45225</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10723,7 +10723,7 @@
         <v>45672</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10833,7 +10833,7 @@
         <v>45982</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10947,7 +10947,7 @@
         <v>45985</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -11057,7 +11057,7 @@
         <v>45608</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -11167,7 +11167,7 @@
         <v>46027</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -11272,7 +11272,7 @@
         <v>45572</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -11382,7 +11382,7 @@
         <v>45600</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -11487,7 +11487,7 @@
         <v>46197</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -11597,7 +11597,7 @@
         <v>46199</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11707,7 +11707,7 @@
         <v>46199</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11817,7 +11817,7 @@
         <v>45222</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11922,7 +11922,7 @@
         <v>44865</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -12036,7 +12036,7 @@
         <v>45915</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -12146,7 +12146,7 @@
         <v>46276</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -12256,7 +12256,7 @@
         <v>46240</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -12366,7 +12366,7 @@
         <v>45918</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -12471,7 +12471,7 @@
         <v>46272</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -12581,7 +12581,7 @@
         <v>45799</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -12695,7 +12695,7 @@
         <v>45819</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -12805,7 +12805,7 @@
         <v>45826</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -12915,7 +12915,7 @@
         <v>45838</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -13025,7 +13025,7 @@
         <v>45876</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -13135,7 +13135,7 @@
         <v>44967</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -13245,7 +13245,7 @@
         <v>45358</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -13350,7 +13350,7 @@
         <v>44820</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -13428,7 +13428,7 @@
         <v>44676</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -13501,7 +13501,7 @@
         <v>44543</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -13579,7 +13579,7 @@
         <v>44543</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -13657,7 +13657,7 @@
         <v>44543</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -13730,7 +13730,7 @@
         <v>44586</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -13808,7 +13808,7 @@
         <v>44586</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -13886,7 +13886,7 @@
         <v>44663</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -13959,7 +13959,7 @@
         <v>44685</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -14037,7 +14037,7 @@
         <v>44539</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -14115,7 +14115,7 @@
         <v>44543</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -14193,7 +14193,7 @@
         <v>44543</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -14271,7 +14271,7 @@
         <v>44638</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -14349,7 +14349,7 @@
         <v>44743</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -14427,7 +14427,7 @@
         <v>44543</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -14505,7 +14505,7 @@
         <v>44586</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -14583,7 +14583,7 @@
         <v>44573</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -14661,7 +14661,7 @@
         <v>44820</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -14739,7 +14739,7 @@
         <v>44824</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -14817,7 +14817,7 @@
         <v>44532</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -14890,7 +14890,7 @@
         <v>44868</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -14968,7 +14968,7 @@
         <v>45028</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -15041,7 +15041,7 @@
         <v>44966</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -15114,7 +15114,7 @@
         <v>45106</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -15192,7 +15192,7 @@
         <v>44841</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -15270,7 +15270,7 @@
         <v>44539</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -15348,7 +15348,7 @@
         <v>45586</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -15421,7 +15421,7 @@
         <v>45596</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -15499,7 +15499,7 @@
         <v>45491</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -15572,7 +15572,7 @@
         <v>45482</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -15645,7 +15645,7 @@
         <v>45463</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -15723,7 +15723,7 @@
         <v>45222</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -15796,7 +15796,7 @@
         <v>45558</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -15874,7 +15874,7 @@
         <v>45086</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -15947,7 +15947,7 @@
         <v>45482</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -16020,7 +16020,7 @@
         <v>45677</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -16098,7 +16098,7 @@
         <v>45349</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -16171,7 +16171,7 @@
         <v>45572</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -16249,7 +16249,7 @@
         <v>44984</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -16322,7 +16322,7 @@
         <v>44984</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -16395,7 +16395,7 @@
         <v>45124</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -16473,7 +16473,7 @@
         <v>44984</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -16551,7 +16551,7 @@
         <v>44984</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -16629,7 +16629,7 @@
         <v>44984</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -16707,7 +16707,7 @@
         <v>45664</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -16785,7 +16785,7 @@
         <v>45679</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -16863,7 +16863,7 @@
         <v>44862</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -16936,7 +16936,7 @@
         <v>44873</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -17014,7 +17014,7 @@
         <v>45257</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -17092,7 +17092,7 @@
         <v>45488</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -17165,7 +17165,7 @@
         <v>45323</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -17238,7 +17238,7 @@
         <v>45124</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -17316,7 +17316,7 @@
         <v>45646</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -17389,7 +17389,7 @@
         <v>45043</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -17467,7 +17467,7 @@
         <v>45516</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -17545,7 +17545,7 @@
         <v>45517</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -17623,7 +17623,7 @@
         <v>44889</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -17701,7 +17701,7 @@
         <v>45596</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -17779,7 +17779,7 @@
         <v>44841</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -17857,7 +17857,7 @@
         <v>44966</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -17935,7 +17935,7 @@
         <v>45884</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -18013,7 +18013,7 @@
         <v>45897</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -18091,7 +18091,7 @@
         <v>46137</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -18169,7 +18169,7 @@
         <v>45474</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -18247,7 +18247,7 @@
         <v>45474</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -18325,7 +18325,7 @@
         <v>45474</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -18403,7 +18403,7 @@
         <v>45904</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -18476,7 +18476,7 @@
         <v>45901</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -18554,7 +18554,7 @@
         <v>45904</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -18632,7 +18632,7 @@
         <v>45491</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -18705,7 +18705,7 @@
         <v>45907</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -18778,7 +18778,7 @@
         <v>45912</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -18856,7 +18856,7 @@
         <v>45918</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -18934,7 +18934,7 @@
         <v>44493</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -19012,7 +19012,7 @@
         <v>45887</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -19090,7 +19090,7 @@
         <v>45928</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -19168,7 +19168,7 @@
         <v>45608</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -19241,7 +19241,7 @@
         <v>45216</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -19319,7 +19319,7 @@
         <v>45028</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -19392,7 +19392,7 @@
         <v>45942</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -19470,7 +19470,7 @@
         <v>45942</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -19548,7 +19548,7 @@
         <v>45943</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -19626,7 +19626,7 @@
         <v>45940</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -19704,7 +19704,7 @@
         <v>45946</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -19782,7 +19782,7 @@
         <v>45951</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -19860,7 +19860,7 @@
         <v>46083</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -19933,7 +19933,7 @@
         <v>45951</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -20011,7 +20011,7 @@
         <v>45951</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -20089,7 +20089,7 @@
         <v>45951</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -20167,7 +20167,7 @@
         <v>45951</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -20245,7 +20245,7 @@
         <v>45951</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -20323,7 +20323,7 @@
         <v>45951</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -20401,7 +20401,7 @@
         <v>45950</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -20474,7 +20474,7 @@
         <v>45950</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -20547,7 +20547,7 @@
         <v>45953</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -20625,7 +20625,7 @@
         <v>44984</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -20703,7 +20703,7 @@
         <v>44984</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -20781,7 +20781,7 @@
         <v>45953</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -20859,7 +20859,7 @@
         <v>45953</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -20937,7 +20937,7 @@
         <v>45953</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -21015,7 +21015,7 @@
         <v>45903</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -21093,7 +21093,7 @@
         <v>44589</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -21166,7 +21166,7 @@
         <v>45960</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -21239,7 +21239,7 @@
         <v>45168</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -21317,7 +21317,7 @@
         <v>45965</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -21395,7 +21395,7 @@
         <v>45842</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -21473,7 +21473,7 @@
         <v>45964</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -21551,7 +21551,7 @@
         <v>45965</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -21629,7 +21629,7 @@
         <v>45967</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -21702,7 +21702,7 @@
         <v>45971</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -21780,7 +21780,7 @@
         <v>45968</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -21853,7 +21853,7 @@
         <v>45973</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -21931,7 +21931,7 @@
         <v>45973</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -22009,7 +22009,7 @@
         <v>45111</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -22082,7 +22082,7 @@
         <v>45972</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -22160,7 +22160,7 @@
         <v>45975</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -22238,7 +22238,7 @@
         <v>45974</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -22316,7 +22316,7 @@
         <v>45974</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -22394,7 +22394,7 @@
         <v>45824</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -22467,7 +22467,7 @@
         <v>45974</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -22545,7 +22545,7 @@
         <v>45974</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -22623,7 +22623,7 @@
         <v>45166</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -22696,7 +22696,7 @@
         <v>46162</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -22774,7 +22774,7 @@
         <v>45974</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -22852,7 +22852,7 @@
         <v>45975</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -22925,7 +22925,7 @@
         <v>45974</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -23003,7 +23003,7 @@
         <v>45979</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -23081,7 +23081,7 @@
         <v>45979</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -23159,7 +23159,7 @@
         <v>46164</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -23237,7 +23237,7 @@
         <v>45985</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -23315,7 +23315,7 @@
         <v>45985</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -23393,7 +23393,7 @@
         <v>45860</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -23466,7 +23466,7 @@
         <v>45721</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -23539,7 +23539,7 @@
         <v>45883</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -23617,7 +23617,7 @@
         <v>45973</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -23695,7 +23695,7 @@
         <v>45073</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -23773,7 +23773,7 @@
         <v>45995</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -23851,7 +23851,7 @@
         <v>45995</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -23929,7 +23929,7 @@
         <v>45113</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -24007,7 +24007,7 @@
         <v>45994</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -24085,7 +24085,7 @@
         <v>45953</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -24163,7 +24163,7 @@
         <v>46170</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -24241,7 +24241,7 @@
         <v>46170</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -24314,7 +24314,7 @@
         <v>46006</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -24387,7 +24387,7 @@
         <v>45474</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -24465,7 +24465,7 @@
         <v>45474</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -24543,7 +24543,7 @@
         <v>45397</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -24621,7 +24621,7 @@
         <v>46010</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -24694,7 +24694,7 @@
         <v>44868</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -24767,7 +24767,7 @@
         <v>45572</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -24845,7 +24845,7 @@
         <v>46021</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -24918,7 +24918,7 @@
         <v>46010</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -24991,7 +24991,7 @@
         <v>46010</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -25069,7 +25069,7 @@
         <v>46009</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -25142,7 +25142,7 @@
         <v>45993</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -25220,7 +25220,7 @@
         <v>45992</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -25298,7 +25298,7 @@
         <v>45994</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -25376,7 +25376,7 @@
         <v>46030</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -25454,7 +25454,7 @@
         <v>46177</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -25532,7 +25532,7 @@
         <v>45693</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -25605,7 +25605,7 @@
         <v>46177</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -25683,7 +25683,7 @@
         <v>46178</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -25761,7 +25761,7 @@
         <v>46177</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -25839,7 +25839,7 @@
         <v>45544</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -25917,7 +25917,7 @@
         <v>46177</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -25995,7 +25995,7 @@
         <v>45604</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -26073,7 +26073,7 @@
         <v>45678</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -26151,7 +26151,7 @@
         <v>45883</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -26229,7 +26229,7 @@
         <v>45090</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -26302,7 +26302,7 @@
         <v>45572</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -26380,7 +26380,7 @@
         <v>46183</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -26458,7 +26458,7 @@
         <v>45474</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -26536,7 +26536,7 @@
         <v>45526</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -26609,7 +26609,7 @@
         <v>44802</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -26682,7 +26682,7 @@
         <v>46077</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -26760,7 +26760,7 @@
         <v>46077</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -26838,7 +26838,7 @@
         <v>44851</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -26911,7 +26911,7 @@
         <v>46077</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -26989,7 +26989,7 @@
         <v>46077</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -27067,7 +27067,7 @@
         <v>45534</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -27145,7 +27145,7 @@
         <v>46185</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -27223,7 +27223,7 @@
         <v>46092</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -27301,7 +27301,7 @@
         <v>46092</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -27379,7 +27379,7 @@
         <v>46092</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -27457,7 +27457,7 @@
         <v>46092</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -27535,7 +27535,7 @@
         <v>46191</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -27613,7 +27613,7 @@
         <v>46191</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -27691,7 +27691,7 @@
         <v>46192</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -27769,7 +27769,7 @@
         <v>45113</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -27847,7 +27847,7 @@
         <v>46106</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -27925,7 +27925,7 @@
         <v>46106</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -28003,7 +28003,7 @@
         <v>46108</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -28081,7 +28081,7 @@
         <v>46198</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -28154,7 +28154,7 @@
         <v>46108</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -28232,7 +28232,7 @@
         <v>46108</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -28310,7 +28310,7 @@
         <v>45986</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -28383,7 +28383,7 @@
         <v>46106</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -28461,7 +28461,7 @@
         <v>45613</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -28534,7 +28534,7 @@
         <v>45763</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -28612,7 +28612,7 @@
         <v>45224</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -28690,7 +28690,7 @@
         <v>46113</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -28768,7 +28768,7 @@
         <v>46113</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -28846,7 +28846,7 @@
         <v>46113</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -28924,7 +28924,7 @@
         <v>46114</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -29002,7 +29002,7 @@
         <v>46113</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -29080,7 +29080,7 @@
         <v>46197</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -29158,7 +29158,7 @@
         <v>45474</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -29236,7 +29236,7 @@
         <v>46197</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -29314,7 +29314,7 @@
         <v>46197</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -29392,7 +29392,7 @@
         <v>46113</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -29470,7 +29470,7 @@
         <v>46113</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -29548,7 +29548,7 @@
         <v>45993</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -29626,7 +29626,7 @@
         <v>46199</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -29704,7 +29704,7 @@
         <v>45572</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -29782,7 +29782,7 @@
         <v>46199</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -29860,7 +29860,7 @@
         <v>46010</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -29933,7 +29933,7 @@
         <v>46199</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -30011,7 +30011,7 @@
         <v>45505</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -30089,7 +30089,7 @@
         <v>45565</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -30167,7 +30167,7 @@
         <v>45124</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -30245,7 +30245,7 @@
         <v>46204</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -30323,7 +30323,7 @@
         <v>45113</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -30401,7 +30401,7 @@
         <v>45555</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -30474,7 +30474,7 @@
         <v>46205</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -30547,7 +30547,7 @@
         <v>46206</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -30620,7 +30620,7 @@
         <v>46206</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -30693,7 +30693,7 @@
         <v>44866</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -30771,7 +30771,7 @@
         <v>45590</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -30849,7 +30849,7 @@
         <v>46205</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -30922,7 +30922,7 @@
         <v>46212</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -31000,7 +31000,7 @@
         <v>46211</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -31078,7 +31078,7 @@
         <v>46212</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -31156,7 +31156,7 @@
         <v>45520</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -31234,7 +31234,7 @@
         <v>46215</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -31307,7 +31307,7 @@
         <v>46216</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -31380,7 +31380,7 @@
         <v>46216</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -31453,7 +31453,7 @@
         <v>46215</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -31526,7 +31526,7 @@
         <v>45078</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -31604,7 +31604,7 @@
         <v>46175</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -31677,7 +31677,7 @@
         <v>45028</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -31750,7 +31750,7 @@
         <v>45093</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -31828,7 +31828,7 @@
         <v>46009</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -31901,7 +31901,7 @@
         <v>45471</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -31979,7 +31979,7 @@
         <v>44984</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -32057,7 +32057,7 @@
         <v>46274</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -32135,7 +32135,7 @@
         <v>44841</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -32213,7 +32213,7 @@
         <v>44841</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -32291,7 +32291,7 @@
         <v>44984</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -32369,7 +32369,7 @@
         <v>44984</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -32447,7 +32447,7 @@
         <v>44984</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -32525,7 +32525,7 @@
         <v>44984</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -32598,7 +32598,7 @@
         <v>44984</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -32676,7 +32676,7 @@
         <v>45490</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -32749,7 +32749,7 @@
         <v>46281</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -32827,7 +32827,7 @@
         <v>44841</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -32905,7 +32905,7 @@
         <v>46238</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -32983,7 +32983,7 @@
         <v>46281</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -33061,7 +33061,7 @@
         <v>45022</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -33139,7 +33139,7 @@
         <v>46281</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -33217,7 +33217,7 @@
         <v>46281</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -33295,7 +33295,7 @@
         <v>45576</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -33373,7 +33373,7 @@
         <v>46237</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -33446,7 +33446,7 @@
         <v>46281</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -33524,7 +33524,7 @@
         <v>46077</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -33597,7 +33597,7 @@
         <v>45555</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -33675,7 +33675,7 @@
         <v>46288</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -33753,7 +33753,7 @@
         <v>46289</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -33831,7 +33831,7 @@
         <v>45490</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -33904,7 +33904,7 @@
         <v>45490</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -33977,7 +33977,7 @@
         <v>45490</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -34050,7 +34050,7 @@
         <v>45490</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -34123,7 +34123,7 @@
         <v>46248</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -34196,7 +34196,7 @@
         <v>46170</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -34269,7 +34269,7 @@
         <v>44854</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -34347,7 +34347,7 @@
         <v>46247</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -34420,7 +34420,7 @@
         <v>46174</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -34498,7 +34498,7 @@
         <v>45057</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -34576,7 +34576,7 @@
         <v>45073</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -34654,7 +34654,7 @@
         <v>46253</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -34727,7 +34727,7 @@
         <v>45565</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -34800,7 +34800,7 @@
         <v>46294</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -34878,7 +34878,7 @@
         <v>46295</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -34956,7 +34956,7 @@
         <v>46254</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -35034,7 +35034,7 @@
         <v>46255</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -35107,7 +35107,7 @@
         <v>46301</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -35185,7 +35185,7 @@
         <v>46301</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -35263,7 +35263,7 @@
         <v>46300</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -35341,7 +35341,7 @@
         <v>46300</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -35419,7 +35419,7 @@
         <v>46300</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -35497,7 +35497,7 @@
         <v>46300</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -35575,7 +35575,7 @@
         <v>45451</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -35653,7 +35653,7 @@
         <v>46303</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -35731,7 +35731,7 @@
         <v>46300</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -35809,7 +35809,7 @@
         <v>46304</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -35887,7 +35887,7 @@
         <v>45544</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -35965,7 +35965,7 @@
         <v>45259</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -36043,7 +36043,7 @@
         <v>45596</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -36121,7 +36121,7 @@
         <v>46266</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -36199,7 +36199,7 @@
         <v>45532</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -36272,7 +36272,7 @@
         <v>46248</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -36345,7 +36345,7 @@
         <v>46310</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -36423,7 +36423,7 @@
         <v>45813</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -36496,7 +36496,7 @@
         <v>45590</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -36574,7 +36574,7 @@
         <v>45819</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -36652,7 +36652,7 @@
         <v>45824</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -36725,7 +36725,7 @@
         <v>45827</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -36803,7 +36803,7 @@
         <v>45826</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -36881,7 +36881,7 @@
         <v>45838</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -36959,7 +36959,7 @@
         <v>45868</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -37032,7 +37032,7 @@
         <v>45807</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -37110,7 +37110,7 @@
         <v>45880</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -37188,7 +37188,7 @@
         <v>45883</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -37266,7 +37266,7 @@
         <v>44823</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -37344,7 +37344,7 @@
         <v>44820</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -37417,7 +37417,7 @@
         <v>45392</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -37490,7 +37490,7 @@
         <v>44823</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -37568,7 +37568,7 @@
         <v>45327</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -37641,7 +37641,7 @@
         <v>45327</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -37714,7 +37714,7 @@
         <v>44824</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -37792,7 +37792,7 @@
         <v>45756</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -37865,7 +37865,7 @@
         <v>45841</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -37943,7 +37943,7 @@
         <v>46147</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -38016,7 +38016,7 @@
         <v>46147</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -38089,7 +38089,7 @@
         <v>46147</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -38162,7 +38162,7 @@
         <v>46148</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -38235,7 +38235,7 @@
         <v>46148</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
